--- a/Results/Phase 2/Carbon dioxide/carbon dioxide eutrophication marine results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide eutrophication marine results.xlsx
@@ -2641,7 +2641,7 @@
         <v>-8.099982488104231e-06</v>
       </c>
       <c r="S8" t="n">
-        <v>-7.138816863497795e-06</v>
+        <v>-7.138816863497801e-06</v>
       </c>
       <c r="T8" t="n">
         <v>-8.099982488104231e-06</v>
@@ -2690,7 +2690,7 @@
         <v>1.607141153598517e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>5.020030017606605e-05</v>
+        <v>5.020030017606604e-05</v>
       </c>
       <c r="G9" t="n">
         <v>5.611192243997533e-05</v>
@@ -3278,7 +3278,7 @@
         <v>0.0001009452155653454</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.942347021634832e-05</v>
+        <v>1.942347021634833e-05</v>
       </c>
       <c r="AA15" t="n">
         <v>8.70738463727944e-05</v>
@@ -3327,7 +3327,7 @@
         <v>-6.860823250690043e-06</v>
       </c>
       <c r="M16" t="n">
-        <v>-6.86082325069026e-06</v>
+        <v>-6.860823250690267e-06</v>
       </c>
       <c r="N16" t="n">
         <v>-1.228054661498843e-05</v>
@@ -5014,85 +5014,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0002960307359406516</v>
+        <v>0.0002960307359406476</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001045586153791281</v>
+        <v>0.000104558615379128</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000409189143460817</v>
+        <v>0.0004091891434608133</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001757370008529381</v>
+        <v>0.000175737000852938</v>
       </c>
       <c r="F2" t="n">
         <v>0.0001777452791468579</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0003747709123372867</v>
+        <v>0.0003747709123372841</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000129543865580332</v>
+        <v>0.0001295438655803292</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0003852242073481796</v>
+        <v>0.0003852242073481756</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0003883624642507696</v>
+        <v>0.0003883624642507645</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004649088928065454</v>
+        <v>0.0004649088928065417</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000340934407042798</v>
+        <v>0.0003409344070427915</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00104343646121261</v>
+        <v>0.001043436461212608</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0002728693055101522</v>
+        <v>0.0002728693055101488</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0002569226500327296</v>
+        <v>0.0002569226500327276</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0003690009022679432</v>
+        <v>0.0003690009022679412</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0001834932490540726</v>
+        <v>0.0001834932490540695</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0001312866864511078</v>
+        <v>0.0001312866864511048</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0003598813391129546</v>
+        <v>0.000359881339112952</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0003171192989499676</v>
+        <v>0.0003171192989499639</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0003787073417644168</v>
+        <v>0.0003787073417644116</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00019011951834279</v>
+        <v>0.0001901195183427897</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0003710926262078079</v>
+        <v>0.0003710926262078049</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0003926413587856811</v>
+        <v>0.0003926413587856772</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0004607587174204128</v>
+        <v>0.0004607587174204098</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0002097463503450982</v>
+        <v>0.0002097463503450943</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0004424551322414349</v>
+        <v>0.0004424551322414308</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.000575986324572151</v>
+        <v>0.0005759863245721505</v>
       </c>
     </row>
     <row r="3">
@@ -5102,85 +5102,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.134097306722312e-05</v>
+        <v>4.134097306721897e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>5.574543155556619e-05</v>
+        <v>5.574543155556627e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>5.61739785815048e-05</v>
+        <v>5.617397858150623e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.698050289578369e-05</v>
+        <v>4.698050289578378e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>4.288962584359476e-05</v>
+        <v>4.28896258435948e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>5.924969890279042e-05</v>
+        <v>5.924969890279119e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>5.61739785815048e-05</v>
+        <v>5.617397858150623e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>5.61739785815048e-05</v>
+        <v>5.617397858150623e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>5.565559813845837e-05</v>
+        <v>5.565559813845661e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>5.61739785815048e-05</v>
+        <v>5.617397858150623e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>5.61739785815048e-05</v>
+        <v>5.617397858150623e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>5.767058870098189e-05</v>
+        <v>5.767058870098197e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.467591779960245e-05</v>
+        <v>4.46759177996014e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>4.783568473735555e-05</v>
+        <v>4.783568473735527e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>4.706114951035624e-05</v>
+        <v>4.706114951035771e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.842594893740645e-05</v>
+        <v>3.842594893740167e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>5.61739785815048e-05</v>
+        <v>5.617397858150623e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>5.61739785815048e-05</v>
+        <v>5.617397858150623e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>5.61739785815048e-05</v>
+        <v>5.617397858150623e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>4.892443141877447e-05</v>
+        <v>4.892443141877237e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>5.064956766205533e-05</v>
+        <v>5.064956766205494e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>5.617689368993694e-05</v>
+        <v>5.617689368993415e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>3.978542336509705e-05</v>
+        <v>3.978542336509415e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.090541012988464e-05</v>
+        <v>7.090541012988468e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.106544237468525e-05</v>
+        <v>4.106544237468428e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.61739785815048e-05</v>
+        <v>5.617397858150623e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.231544764670931e-05</v>
+        <v>7.231544764670935e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5190,85 +5190,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0004739712368440766</v>
+        <v>0.0004739712368440705</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0004039095506113215</v>
+        <v>0.0004039095506113184</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0005152161476120696</v>
+        <v>0.0005152161476120625</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004293023805849179</v>
+        <v>0.000429302380584917</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004303732176532653</v>
+        <v>0.0004303732176532607</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0005026711065268176</v>
+        <v>0.00050267110652681</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0004132887275852739</v>
+        <v>0.0004132887275852692</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0005064812098095</v>
+        <v>0.0005064812098094928</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0004968972555304</v>
+        <v>0.000496897255530393</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0005355253419542548</v>
+        <v>0.0005355253419542499</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004903380976752832</v>
+        <v>0.0004903380976752725</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0007473429605295834</v>
+        <v>0.0007473429605295758</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0004655291674274055</v>
+        <v>0.0004655291674274001</v>
       </c>
       <c r="O4" t="n">
-        <v>0.000459716798760969</v>
+        <v>0.0004597167987609639</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0005005680056114188</v>
+        <v>0.0005005680056114106</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0004329526443558105</v>
+        <v>0.0004329526443558017</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0004139239653274374</v>
+        <v>0.0004139239653274297</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0004972440319287447</v>
+        <v>0.0004972440319287346</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0004816577704265644</v>
+        <v>0.000481657770426556</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0005041058888291213</v>
+        <v>0.0005041058888291156</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0003650649787460433</v>
+        <v>0.0003650649787460454</v>
       </c>
       <c r="W4" t="n">
-        <v>0.000501330414425238</v>
+        <v>0.000501330414425231</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0005091846744118788</v>
+        <v>0.0005091846744118753</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0005340126517598305</v>
+        <v>0.000534012651759824</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0004425215914969073</v>
+        <v>0.0004425215914968983</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0005273412098936423</v>
+        <v>0.0005273412098936344</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.000576423035774559</v>
+        <v>0.0005764230357745492</v>
       </c>
     </row>
     <row r="5">
@@ -5278,85 +5278,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.000381139808994898</v>
+        <v>0.0003811398089948946</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0003861177183009778</v>
+        <v>0.0003861177183009724</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0003865462653269142</v>
+        <v>0.0003865462653269079</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0003823721490146688</v>
+        <v>0.0003823721490146693</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0003812199155792618</v>
+        <v>0.0003812199155792505</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0003876673292670894</v>
+        <v>0.0003876673292670876</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0003865462653269142</v>
+        <v>0.0003865462653269079</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003865462653269142</v>
+        <v>0.0003865462653269079</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003756295096737229</v>
+        <v>0.0003756295096737231</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003865462653269142</v>
+        <v>0.0003865462653269079</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003865462653269142</v>
+        <v>0.0003865462653269079</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003880428754463904</v>
+        <v>0.0003880428754463831</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0003823553571889606</v>
+        <v>0.0003823553571889522</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0003835070551339139</v>
+        <v>0.000383507055133907</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0003832247461387243</v>
+        <v>0.0003832247461387163</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0003800773169295229</v>
+        <v>0.0003800773169295161</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0003865462653269142</v>
+        <v>0.0003865462653269079</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003865462653269142</v>
+        <v>0.0003865462653269079</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003865462653269142</v>
+        <v>0.0003865462653269079</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0003839038905145758</v>
+        <v>0.0003839038905145765</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003142298194617642</v>
+        <v>0.0003142298194617694</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003865473278497071</v>
+        <v>0.0003865473278496993</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0003805728293946676</v>
+        <v>0.0003805728293946575</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0003919156991410908</v>
+        <v>0.0003919156991410875</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.000381039381292922</v>
+        <v>0.0003810393812929103</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0003865462653269142</v>
+        <v>0.0003865462653269079</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.000392840915537271</v>
+        <v>0.0003928409155372707</v>
       </c>
     </row>
     <row r="6">
@@ -5366,82 +5366,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0001234872540763666</v>
+        <v>0.0001234872540763646</v>
       </c>
       <c r="C6" t="n">
-        <v>5.342556784360789e-05</v>
+        <v>5.342556784360793e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001647321648443592</v>
+        <v>0.000164732164844357</v>
       </c>
       <c r="E6" t="n">
-        <v>7.881839781721037e-05</v>
+        <v>7.881839781721051e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>7.988923488555246e-05</v>
+        <v>7.988923488555257e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001480363865035294</v>
+        <v>0.0001480363865035253</v>
       </c>
       <c r="H6" t="n">
-        <v>6.280474481756478e-05</v>
+        <v>6.280474481756306e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001559972270417902</v>
+        <v>0.0001559972270417879</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001528278868402047</v>
+        <v>0.0001528278868402035</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0001850413591865464</v>
+        <v>0.000185041359186545</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001398541149075716</v>
+        <v>0.0001398541149075685</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0003968589777618705</v>
+        <v>0.0003968589777618701</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001150451846596964</v>
+        <v>0.0001150451846596952</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0001050820787376799</v>
+        <v>0.0001050820787376775</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0001459332855881309</v>
+        <v>0.0001459332855881295</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.246866158809827e-05</v>
+        <v>8.246866158809629e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>6.343998255972649e-05</v>
+        <v>6.343998255972464e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001467600491610345</v>
+        <v>0.0001467600491610322</v>
       </c>
       <c r="T6" t="n">
-        <v>0.000131173787658852</v>
+        <v>0.0001311737876588509</v>
       </c>
       <c r="U6" t="n">
-        <v>0.000149471168805829</v>
+        <v>0.0001494711688058266</v>
       </c>
       <c r="V6" t="n">
-        <v>8.00635539833765e-05</v>
+        <v>8.006355398337687e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>0.000146695694401949</v>
+        <v>0.000146695694401947</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0001545499543885907</v>
+        <v>0.0001545499543885884</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001835286689921208</v>
+        <v>0.0001835286689921184</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.203760872919737e-05</v>
+        <v>9.203760872919483e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0001768572271259314</v>
+        <v>0.0001768572271259297</v>
       </c>
       <c r="AB6" t="n">
         <v>0.0002259390530068434</v>
@@ -5454,85 +5454,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.065582622719223e-05</v>
+        <v>3.065582622719011e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>3.563373553326333e-05</v>
+        <v>3.563373553326339e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>3.606228255920216e-05</v>
+        <v>3.606228255920213e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>3.188816624696102e-05</v>
+        <v>3.188816624696103e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>3.073593281154454e-05</v>
+        <v>3.073593281154457e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>3.303260924379946e-05</v>
+        <v>3.303260924380188e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>3.606228255920216e-05</v>
+        <v>3.606228255920213e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.606228255920216e-05</v>
+        <v>3.606228255920213e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.156014098353964e-05</v>
+        <v>3.156014098353566e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.606228255920216e-05</v>
+        <v>3.606228255920213e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.606228255920216e-05</v>
+        <v>3.606228255920213e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.755889267867574e-05</v>
+        <v>3.755889267867576e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.187137442124745e-05</v>
+        <v>3.187137442124333e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.887233511062277e-05</v>
+        <v>2.887233511062078e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.859002611543486e-05</v>
+        <v>2.859002611543182e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.959333416181169e-05</v>
+        <v>2.959333416181352e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>3.606228255920216e-05</v>
+        <v>3.606228255920213e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.606228255920216e-05</v>
+        <v>3.606228255920213e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>3.606228255920216e-05</v>
+        <v>3.606228255920213e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.926917049128793e-05</v>
+        <v>2.926917049128878e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.922839469909552e-05</v>
+        <v>2.922839469909559e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>3.191260782641544e-05</v>
+        <v>3.191260782641569e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.593810937137761e-05</v>
+        <v>2.59381093713738e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.143171637338061e-05</v>
+        <v>4.143171637338424e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.055539852520797e-05</v>
+        <v>3.05553985252044e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.606228255920216e-05</v>
+        <v>3.606228255920213e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.235693276956247e-05</v>
+        <v>4.235693276956248e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5542,85 +5542,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>1.715047382543838e-05</v>
+        <v>1.715047382543853e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.623289662620071e-05</v>
+        <v>1.623289662620079e-05</v>
       </c>
     </row>
     <row r="9">
@@ -5630,85 +5630,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0002738207759786874</v>
+        <v>0.0002738207759786854</v>
       </c>
       <c r="C9" t="n">
-        <v>6.850567630908145e-05</v>
+        <v>6.85056763090815e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0003954324548668529</v>
+        <v>0.0003954324548668539</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0001459328426224653</v>
+        <v>0.0001459328426224655</v>
       </c>
       <c r="F9" t="n">
         <v>0.0001475181333738571</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0003584430789731746</v>
+        <v>0.0003584430789731752</v>
       </c>
       <c r="H9" t="n">
-        <v>9.489683863230286e-05</v>
+        <v>9.489683863230297e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0003696772663751254</v>
+        <v>0.0003696772663751253</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0003736070654632673</v>
+        <v>0.0003736070654632669</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0004553146360821919</v>
+        <v>0.0004553146360821925</v>
       </c>
       <c r="L9" t="n">
-        <v>0.000322078885567239</v>
+        <v>0.0003220788855672387</v>
       </c>
       <c r="M9" t="n">
         <v>0.001075451532186656</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0002489291174459133</v>
+        <v>0.000248929117445913</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0002317911991262791</v>
+        <v>0.0002317911991262793</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0003522420319002071</v>
+        <v>0.0003522420319002072</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.000152876402351895</v>
+        <v>0.0001528764023518954</v>
       </c>
       <c r="R9" t="n">
-        <v>9.676985343289225e-05</v>
+        <v>9.676985343289233e-05</v>
       </c>
       <c r="S9" t="n">
         <v>0.0003424412101114496</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0002964847176963598</v>
+        <v>0.0002964847176963592</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0003626735714478302</v>
+        <v>0.0003626735714478316</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0001615662750214288</v>
+        <v>0.0001615662750214295</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0003544900138723127</v>
+        <v>0.0003544900138723124</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0003776485012011509</v>
+        <v>0.0003776485012011515</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0004508544301863279</v>
+        <v>0.0004508544301863281</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0001810906888020974</v>
+        <v>0.0001810906888020972</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0004311835124695752</v>
+        <v>0.0004311835124695747</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0005739943852379372</v>
+        <v>0.0005739943852379369</v>
       </c>
     </row>
     <row r="10">
@@ -5718,85 +5718,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.049263353750763e-07</v>
+        <v>1.049263353751644e-07</v>
       </c>
       <c r="C10" t="n">
-        <v>1.604600170998365e-05</v>
+        <v>1.604600170998377e-05</v>
       </c>
       <c r="D10" t="n">
-        <v>1.604600170998365e-05</v>
+        <v>1.604600170998377e-05</v>
       </c>
       <c r="E10" t="n">
-        <v>7.557849305775843e-06</v>
+        <v>7.55784930577591e-06</v>
       </c>
       <c r="F10" t="n">
-        <v>2.588359571167637e-06</v>
+        <v>2.588359571167759e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>1.93514875352013e-05</v>
+        <v>1.935148753520137e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>1.604600170998365e-05</v>
+        <v>1.604600170998377e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>1.604600170998365e-05</v>
+        <v>1.604600170998377e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>1.604600170998365e-05</v>
+        <v>1.604600170998377e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>1.604600170998365e-05</v>
+        <v>1.604600170998377e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>1.604600170998365e-05</v>
+        <v>1.604600170998377e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>1.604600170998944e-05</v>
+        <v>1.604600170998953e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>3.689001410238813e-06</v>
+        <v>3.689001410238894e-06</v>
       </c>
       <c r="O10" t="n">
-        <v>7.084812385459348e-06</v>
+        <v>7.084812385459361e-06</v>
       </c>
       <c r="P10" t="n">
-        <v>6.2524170612638e-06</v>
+        <v>6.252417061263922e-06</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.027858812413712e-06</v>
+        <v>-3.027858812413637e-06</v>
       </c>
       <c r="R10" t="n">
-        <v>1.604600170998365e-05</v>
+        <v>1.604600170998377e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>1.604600170998365e-05</v>
+        <v>1.604600170998377e-05</v>
       </c>
       <c r="T10" t="n">
-        <v>1.604600170998365e-05</v>
+        <v>1.604600170998377e-05</v>
       </c>
       <c r="U10" t="n">
-        <v>8.254891699163861e-06</v>
+        <v>8.254891699163983e-06</v>
       </c>
       <c r="V10" t="n">
-        <v>1.167750203113097e-05</v>
+        <v>1.167750203113105e-05</v>
       </c>
       <c r="W10" t="n">
-        <v>1.604913458572831e-05</v>
+        <v>1.60491345857284e-05</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.56682758035365e-06</v>
+        <v>-1.566827580353576e-06</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.187791523974201e-05</v>
+        <v>3.187791523974211e-05</v>
       </c>
       <c r="Z10" t="n">
-        <v>-1.911873236870918e-07</v>
+        <v>-1.911873236870037e-07</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.604600170998365e-05</v>
+        <v>1.604600170998377e-05</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.269778790767041e-05</v>
+        <v>3.269778790767049e-05</v>
       </c>
     </row>
     <row r="11">
@@ -5806,85 +5806,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0002912746559328212</v>
+        <v>0.00029127465593281</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0003006669541940286</v>
+        <v>0.0003006669541940226</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0002405620300887506</v>
+        <v>0.0002405620300887434</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0003002159416632579</v>
+        <v>0.000300215941663246</v>
       </c>
     </row>
     <row r="12">
@@ -5894,85 +5894,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0004268269357675641</v>
+        <v>0.0004268269357675617</v>
       </c>
       <c r="C12" t="n">
-        <v>0.000325909342365502</v>
+        <v>0.0003259093423654956</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0004866021689711979</v>
+        <v>0.0004866021689711928</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0003639667638647585</v>
+        <v>0.0003639667638647498</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0003647459745888074</v>
+        <v>0.0003647459745888084</v>
       </c>
       <c r="G12" t="n">
-        <v>0.000468420949944243</v>
+        <v>0.0004684209499442408</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0003388812698712158</v>
+        <v>0.0003388812698712071</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0004739428387788056</v>
+        <v>0.0004739428387787998</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0004669331492493586</v>
+        <v>0.0004669331492493526</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0005160357840615801</v>
+        <v>0.0005160357840615761</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0004505470240106914</v>
+        <v>0.0004505470240106878</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0008208488408479336</v>
+        <v>0.0008208488408479245</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0004145920525127241</v>
+        <v>0.0004145920525127194</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0004061683297786364</v>
+        <v>0.00040616832977863</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0004653729775925588</v>
+        <v>0.000465372977592551</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0003673797000719077</v>
+        <v>0.0003673797000719048</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0003398019042833278</v>
+        <v>0.0003398019042833218</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0004605556244126131</v>
+        <v>0.0004605556244126098</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0004379668395487913</v>
+        <v>0.000437966839548785</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0004705003445924433</v>
+        <v>0.0004705003445924368</v>
       </c>
       <c r="V12" t="n">
-        <v>0.000311997081929748</v>
+        <v>0.0003119970819297471</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0004664779179062569</v>
+        <v>0.0004664779179062503</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0004778609034334736</v>
+        <v>0.000477860903433469</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0005138434794244004</v>
+        <v>0.0005138434794243949</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0003812477394547557</v>
+        <v>0.0003812477394547513</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0005041747230631816</v>
+        <v>0.0005041747230631775</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0005743698992320248</v>
+        <v>0.0005743698992320194</v>
       </c>
     </row>
     <row r="13">
@@ -5982,85 +5982,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0002922886340720013</v>
+        <v>0.000292288634071992</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0003001240780585132</v>
+        <v>0.0003001240780585031</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0003001240780585132</v>
+        <v>0.0003001240780585031</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0002959519352670642</v>
+        <v>0.0002959519352670582</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0002935093046701879</v>
+        <v>0.0002935093046701869</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0003017488084122102</v>
+        <v>0.0003017488084122049</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0003001240780585132</v>
+        <v>0.0003001240780585031</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0003001240780585132</v>
+        <v>0.0003001240780585031</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0002911827923280759</v>
+        <v>0.0002911827923280699</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0003001240780585132</v>
+        <v>0.0003001240780585031</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0003001240780585132</v>
+        <v>0.0003001240780585031</v>
       </c>
       <c r="M13" t="n">
-        <v>0.000300124078058516</v>
+        <v>0.000300124078058506</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0002940502981274431</v>
+        <v>0.0002940502981274361</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0002957194255896662</v>
+        <v>0.0002957194255896642</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0002953102821169642</v>
+        <v>0.0002953102821169559</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0002907487904936688</v>
+        <v>0.0002907487904936684</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0003001240780585132</v>
+        <v>0.0003001240780585031</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0003001240780585132</v>
+        <v>0.0003001240780585031</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0003001240780585132</v>
+        <v>0.0003001240780585031</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0002962945493317501</v>
+        <v>0.0002962945493317506</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0002383229377849147</v>
+        <v>0.0002383229377849103</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0003001256179466214</v>
+        <v>0.0003001256179466157</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0002914669245036024</v>
+        <v>0.0002914669245035943</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.0003079058662218953</v>
+        <v>0.0003079058662218949</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0002921430866773146</v>
+        <v>0.0002921430866773102</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0003001240780585132</v>
+        <v>0.0003001240780585031</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0003083088544905451</v>
+        <v>0.0003083088544905432</v>
       </c>
     </row>
     <row r="14">
@@ -6070,85 +6070,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-1.155631129757985e-06</v>
+        <v>-1.15563112975791e-06</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.155631129757985e-06</v>
+        <v>-1.15563112975791e-06</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.155631129757985e-06</v>
+        <v>-1.15563112975791e-06</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.155631129757985e-06</v>
+        <v>-1.15563112975791e-06</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.155631129757985e-06</v>
+        <v>-1.15563112975791e-06</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.724736357010182e-06</v>
+        <v>-4.724736357010114e-06</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.155631129757985e-06</v>
+        <v>-1.15563112975791e-06</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.155631129757985e-06</v>
+        <v>-1.15563112975791e-06</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.58115816470013e-06</v>
+        <v>-4.581158164700035e-06</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.155631129757985e-06</v>
+        <v>-1.15563112975791e-06</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.155631129757985e-06</v>
+        <v>-1.15563112975791e-06</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.155631129757985e-06</v>
+        <v>-1.15563112975791e-06</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.155631129757985e-06</v>
+        <v>-1.15563112975791e-06</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.724736357010182e-06</v>
+        <v>-4.724736357010114e-06</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.724736357010182e-06</v>
+        <v>-4.724736357010114e-06</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.155631129757985e-06</v>
+        <v>-1.15563112975791e-06</v>
       </c>
       <c r="R14" t="n">
-        <v>-1.155631129757985e-06</v>
+        <v>-1.15563112975791e-06</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.046185989860462e-07</v>
+        <v>-7.046185989860259e-07</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.155631129757985e-06</v>
+        <v>-1.15563112975791e-06</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.724736357010182e-06</v>
+        <v>-4.724736357010107e-06</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.502885432997523e-06</v>
+        <v>-4.502885432997537e-06</v>
       </c>
       <c r="W14" t="n">
-        <v>-4.724736357010182e-06</v>
+        <v>-4.724736357010114e-06</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.724736357010182e-06</v>
+        <v>-4.724736357010114e-06</v>
       </c>
       <c r="Y14" t="n">
-        <v>-1.155631129757985e-06</v>
+        <v>-1.15563112975791e-06</v>
       </c>
       <c r="Z14" t="n">
-        <v>-1.155631129757985e-06</v>
+        <v>-1.15563112975791e-06</v>
       </c>
       <c r="AA14" t="n">
-        <v>-1.155631129757985e-06</v>
+        <v>-1.15563112975791e-06</v>
       </c>
       <c r="AB14" t="n">
-        <v>-1.155631129757985e-06</v>
+        <v>-1.15563112975791e-06</v>
       </c>
     </row>
     <row r="15">
@@ -6158,85 +6158,85 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0001254553629745501</v>
+        <v>0.0001254553629745502</v>
       </c>
       <c r="C15" t="n">
-        <v>2.453776957248709e-05</v>
+        <v>2.453776957248721e-05</v>
       </c>
       <c r="D15" t="n">
         <v>0.0001852305961781846</v>
       </c>
       <c r="E15" t="n">
-        <v>6.259519107174345e-05</v>
+        <v>6.259519107174372e-05</v>
       </c>
       <c r="F15" t="n">
-        <v>6.337440179579871e-05</v>
+        <v>6.337440179579875e-05</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0001634802719239779</v>
+        <v>0.0001634802719239771</v>
       </c>
       <c r="H15" t="n">
-        <v>3.750969707820177e-05</v>
+        <v>3.750969707820195e-05</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0001725712659857915</v>
+        <v>0.0001725712659857917</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0001710773351518458</v>
+        <v>0.000171077335151845</v>
       </c>
       <c r="K15" t="n">
         <v>0.0002146642112685652</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0001491754512176782</v>
+        <v>0.0001491754512176769</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0005194772680549212</v>
+        <v>0.000519477268054921</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0001132204797197099</v>
+        <v>0.0001132204797197098</v>
       </c>
       <c r="O15" t="n">
-        <v>0.000101227651758369</v>
+        <v>0.0001012276517583694</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0001604322995722905</v>
+        <v>0.0001604322995722908</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.600812727889575e-05</v>
+        <v>6.600812727889577e-05</v>
       </c>
       <c r="R15" t="n">
-        <v>3.843033149031334e-05</v>
+        <v>3.843033149031329e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0001591840516195984</v>
+        <v>0.0001591840516195981</v>
       </c>
       <c r="T15" t="n">
         <v>0.0001365952667557758</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0001655596665721774</v>
+        <v>0.0001655596665721771</v>
       </c>
       <c r="V15" t="n">
-        <v>6.693216640799973e-05</v>
+        <v>6.69321664079997e-05</v>
       </c>
       <c r="W15" t="n">
-        <v>0.0001615372398859891</v>
+        <v>0.0001615372398859893</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0001729202254132079</v>
+        <v>0.0001729202254132082</v>
       </c>
       <c r="Y15" t="n">
         <v>0.0002124719066313871</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.987616666174078e-05</v>
+        <v>7.987616666174084e-05</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.0002028031502701689</v>
+        <v>0.0002028031502701686</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.0002729983264390106</v>
+        <v>0.0002729983264390108</v>
       </c>
     </row>
     <row r="16">
@@ -6246,85 +6246,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-9.082938721012786e-06</v>
+        <v>-9.082938721012711e-06</v>
       </c>
       <c r="C16" t="n">
-        <v>-1.247494734500414e-06</v>
+        <v>-1.247494734500326e-06</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.247494734500414e-06</v>
+        <v>-1.247494734500326e-06</v>
       </c>
       <c r="E16" t="n">
-        <v>-5.419637525951494e-06</v>
+        <v>-5.419637525951454e-06</v>
       </c>
       <c r="F16" t="n">
-        <v>-7.862268122823999e-06</v>
+        <v>-7.862268122823911e-06</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.19186960805522e-06</v>
+        <v>-3.191869608055111e-06</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.247494734500414e-06</v>
+        <v>-1.247494734500326e-06</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.247494734500414e-06</v>
+        <v>-1.247494734500326e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.673021769442559e-06</v>
+        <v>-4.673021769442498e-06</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.247494734500414e-06</v>
+        <v>-1.247494734500326e-06</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.247494734500414e-06</v>
+        <v>-1.247494734500326e-06</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.247494734497581e-06</v>
+        <v>-1.24749473449752e-06</v>
       </c>
       <c r="N16" t="n">
-        <v>-7.321274665570107e-06</v>
+        <v>-7.32127466557006e-06</v>
       </c>
       <c r="O16" t="n">
-        <v>-9.221252430599276e-06</v>
+        <v>-9.221252430599168e-06</v>
       </c>
       <c r="P16" t="n">
-        <v>-9.630395903301164e-06</v>
+        <v>-9.63039590330107e-06</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.062278229934342e-05</v>
+        <v>-1.06227822993434e-05</v>
       </c>
       <c r="R16" t="n">
-        <v>-1.247494734500414e-06</v>
+        <v>-1.247494734500326e-06</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.247494734500414e-06</v>
+        <v>-1.247494734500326e-06</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.247494734500414e-06</v>
+        <v>-1.247494734500326e-06</v>
       </c>
       <c r="U16" t="n">
-        <v>-8.64612868851408e-06</v>
+        <v>-8.646128688514026e-06</v>
       </c>
       <c r="V16" t="n">
-        <v>-6.741977736831983e-06</v>
+        <v>-6.741977736831943e-06</v>
       </c>
       <c r="W16" t="n">
-        <v>-4.815060073643617e-06</v>
+        <v>-4.815060073643611e-06</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.347375351666628e-05</v>
+        <v>-1.347375351666623e-05</v>
       </c>
       <c r="Y16" t="n">
-        <v>6.534293428882722e-06</v>
+        <v>6.53429342888279e-06</v>
       </c>
       <c r="Z16" t="n">
-        <v>-9.228486115695935e-06</v>
+        <v>-9.228486115695868e-06</v>
       </c>
       <c r="AA16" t="n">
-        <v>-1.247494734500414e-06</v>
+        <v>-1.247494734500326e-06</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.937281697532215e-06</v>
+        <v>6.937281697532296e-06</v>
       </c>
     </row>
   </sheetData>
@@ -6490,85 +6490,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0002563455375076418</v>
+        <v>0.0002563455375076417</v>
       </c>
       <c r="C2" t="n">
-        <v>9.460161342395699e-05</v>
+        <v>9.460161342395696e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002773175538347725</v>
+        <v>0.0002773175538347701</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001255513979115395</v>
+        <v>0.0001255513979115397</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002010382488544969</v>
+        <v>0.0002010382488544964</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0003379998732792367</v>
+        <v>0.0003379998732792329</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001242366578448436</v>
+        <v>0.0001242366578448434</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0003642946354521157</v>
+        <v>0.0003642946354521145</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0003611215859185614</v>
+        <v>0.0003611215859185596</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0005406186312555997</v>
+        <v>0.0005406186312556</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003035745367427756</v>
+        <v>0.000303574536742773</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008704442018156458</v>
+        <v>0.0008704442018156448</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0001857671963744234</v>
+        <v>0.0001857671963744217</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00024783892473642</v>
+        <v>0.000247838924736418</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0003281364937306714</v>
+        <v>0.00032813649373067</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0001799382719714142</v>
+        <v>0.000179938271971413</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0001819021700577729</v>
+        <v>0.0001819021700577707</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0003371392706941746</v>
+        <v>0.0003371392706941735</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0003328329261031274</v>
+        <v>0.0003328329261031257</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0003787383358264807</v>
+        <v>0.0003787383358264783</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0002622318284239318</v>
+        <v>0.0002622318284239308</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0002404371927374194</v>
+        <v>0.0002404371927374197</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0004239718364653115</v>
+        <v>0.0004239718364653097</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0006652920859221504</v>
+        <v>0.0006652920859221478</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0001827127070833627</v>
+        <v>0.0001827127070833617</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0004756049310363111</v>
+        <v>0.0004756049310363094</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0005303491350382576</v>
+        <v>0.0005303491350382567</v>
       </c>
     </row>
     <row r="3">
@@ -6578,85 +6578,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.081550191218982e-05</v>
+        <v>4.081550191218673e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>5.518516392307947e-05</v>
+        <v>5.51851639230794e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>5.552642679636535e-05</v>
+        <v>5.552642679636487e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.643556477732183e-05</v>
+        <v>4.643556477732169e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>4.254866109451312e-05</v>
+        <v>4.254866109451307e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>5.857683290371782e-05</v>
+        <v>5.857683290371956e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>5.552642679636535e-05</v>
+        <v>5.552642679636487e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>5.552642679636535e-05</v>
+        <v>5.552642679636487e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>5.509921851286244e-05</v>
+        <v>5.509921851286288e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>5.552642679636535e-05</v>
+        <v>5.552642679636487e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>5.552642679636535e-05</v>
+        <v>5.552642679636487e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>5.666239080426639e-05</v>
+        <v>5.666239080426634e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.412299892645172e-05</v>
+        <v>4.412299892644854e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>4.725675991832759e-05</v>
+        <v>4.7256759918327e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>4.648859937705291e-05</v>
+        <v>4.648859937705352e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.79244694125324e-05</v>
+        <v>3.792446941253309e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>5.552642679636535e-05</v>
+        <v>5.552642679636487e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>5.552642679636535e-05</v>
+        <v>5.552642679636487e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>5.552642679636535e-05</v>
+        <v>5.552642679636487e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>4.833781498057975e-05</v>
+        <v>4.833781498058052e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>5.030463067868848e-05</v>
+        <v>5.030463067868753e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>5.552931791249276e-05</v>
+        <v>5.552931791249275e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>3.927275490792195e-05</v>
+        <v>3.927275490792052e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.013878481928889e-05</v>
+        <v>7.013878481928947e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.05422389300316e-05</v>
+        <v>4.054223893003329e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.552642679636535e-05</v>
+        <v>5.552642679636487e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.151647084527351e-05</v>
+        <v>7.151647084527343e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6666,85 +6666,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0004568517714297911</v>
+        <v>0.0004568517714297985</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0003976811338310519</v>
+        <v>0.0003976811338310571</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004644958251151818</v>
+        <v>0.0004644958251151797</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004083795422016165</v>
+        <v>0.0004083795422016224</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004363378976164842</v>
+        <v>0.0004363378976164877</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004866138179849179</v>
+        <v>0.0004866138179849168</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0004086996360934887</v>
+        <v>0.0004086996360934917</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0004961979500282457</v>
+        <v>0.0004961979500282478</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0004851743237611837</v>
+        <v>0.0004851743237611877</v>
       </c>
       <c r="K4" t="n">
-        <v>0.000560465975997721</v>
+        <v>0.0005604659759977239</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004740661870600889</v>
+        <v>0.0004740661870600881</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0006814054419256464</v>
+        <v>0.0006814054419256493</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0004311267948594578</v>
+        <v>0.0004311267948594571</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0004537512109643719</v>
+        <v>0.0004537512109643698</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0004830187319611154</v>
+        <v>0.0004830187319611142</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0004290022203612469</v>
+        <v>0.0004290022203612464</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0004297180381524683</v>
+        <v>0.0004297180381524707</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0004863001384483684</v>
+        <v>0.0004863001384483671</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0004847305264125831</v>
+        <v>0.0004847305264125824</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0005014625092082079</v>
+        <v>0.0005014625092082073</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0003942205297666746</v>
+        <v>0.0003942205297666731</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0004510533665662609</v>
+        <v>0.0004510533665662679</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0005179495890324816</v>
+        <v>0.0005179495890324805</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0006059079862340613</v>
+        <v>0.0006059079862340604</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0004300134693804909</v>
+        <v>0.0004300134693804882</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0005367692456972019</v>
+        <v>0.0005367692456972093</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0005571189497547148</v>
+        <v>0.0005571189497547124</v>
       </c>
     </row>
     <row r="5">
@@ -6754,85 +6754,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0003782936043367061</v>
+        <v>0.0003782936043367074</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0003833143008393008</v>
+        <v>0.0003833143008393045</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0003836555637125861</v>
+        <v>0.0003836555637125897</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0003795427500492113</v>
+        <v>0.0003795427500492161</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000378570303956672</v>
+        <v>0.0003785703039566773</v>
       </c>
       <c r="G5" t="n">
-        <v>0.000384767400919039</v>
+        <v>0.000384767400919044</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0003836555637125861</v>
+        <v>0.0003836555637125897</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003836555637125861</v>
+        <v>0.0003836555637125897</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003736327643378722</v>
+        <v>0.0003736327643378734</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003836555637125861</v>
+        <v>0.0003836555637125897</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003836555637125861</v>
+        <v>0.0003836555637125897</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003847915277204819</v>
+        <v>0.0003847915277204871</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0003794991481598142</v>
+        <v>0.0003794991481598154</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0003806413672428736</v>
+        <v>0.0003806413672428746</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0003803613817457751</v>
+        <v>0.0003803613817457754</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0003772398569387986</v>
+        <v>0.0003772398569388048</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0003836555637125861</v>
+        <v>0.0003836555637125897</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003836555637125861</v>
+        <v>0.0003836555637125897</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003836555637125861</v>
+        <v>0.0003836555637125897</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0003810353991186745</v>
+        <v>0.0003810353991186795</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003169755547633303</v>
+        <v>0.0003169755547633304</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003836566174904653</v>
+        <v>0.000383656617490472</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0003777312911695005</v>
+        <v>0.0003777312911695004</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0003889815966249709</v>
+        <v>0.0003889815966249766</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0003781940031885254</v>
+        <v>0.0003781940031885219</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0003836555637125861</v>
+        <v>0.0003836555637125897</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.000389879831541538</v>
+        <v>0.0003898798315415363</v>
       </c>
     </row>
     <row r="6">
@@ -6842,85 +6842,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0001088005681848854</v>
+        <v>0.0001088005681848844</v>
       </c>
       <c r="C6" t="n">
-        <v>4.96299305861458e-05</v>
+        <v>4.962993058614578e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001164446218702754</v>
+        <v>0.0001164446218702724</v>
       </c>
       <c r="E6" t="n">
-        <v>6.032833895671014e-05</v>
+        <v>6.032833895671023e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>8.828669437157834e-05</v>
+        <v>8.828669437157809e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001344219357865912</v>
+        <v>0.0001344219357865882</v>
       </c>
       <c r="H6" t="n">
-        <v>6.06484328485821e-05</v>
+        <v>6.064843284858132e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001481467467833393</v>
+        <v>0.0001481467467833369</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001427436065846439</v>
+        <v>0.000142743606584645</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002124147727528149</v>
+        <v>0.0002124147727528155</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001260149838151821</v>
+        <v>0.0001260149838151795</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0003333542386807416</v>
+        <v>0.0003333542386807412</v>
       </c>
       <c r="N6" t="n">
-        <v>8.30755916145518e-05</v>
+        <v>8.307559161454956e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0001015593287660454</v>
+        <v>0.000101559328766043</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0001308268497627893</v>
+        <v>0.0001308268497627859</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.095101711634077e-05</v>
+        <v>8.095101711633803e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>8.166683490756314e-05</v>
+        <v>8.166683490756122e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001382489352034622</v>
+        <v>0.0001382489352034598</v>
       </c>
       <c r="T6" t="n">
-        <v>0.000136679323167677</v>
+        <v>0.0001366793231676748</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001492706270098823</v>
+        <v>0.0001492706270098798</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0001063028439296791</v>
+        <v>0.0001063028439296783</v>
       </c>
       <c r="W6" t="n">
-        <v>9.886148436793489e-05</v>
+        <v>9.886148436793877e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>0.000165757706834155</v>
+        <v>0.0001657577068341523</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0002578567829891549</v>
+        <v>0.0002578567829891515</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.196226613558422e-05</v>
+        <v>8.196226613558198e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0001887180424522965</v>
+        <v>0.000188718042452297</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.000209067746509809</v>
+        <v>0.0002090677465098085</v>
       </c>
     </row>
     <row r="7">
@@ -6930,85 +6930,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.024240109179972e-05</v>
+        <v>3.024240109180071e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>3.526309759439431e-05</v>
+        <v>3.52630975943943e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>3.560436046768025e-05</v>
+        <v>3.560436046768194e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>3.149154680430493e-05</v>
+        <v>3.149154680430489e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>3.051910071176565e-05</v>
+        <v>3.05191007117656e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>3.257551872071316e-05</v>
+        <v>3.257551872071362e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>3.560436046768025e-05</v>
+        <v>3.560436046768194e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.560436046768025e-05</v>
+        <v>3.560436046768194e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.120204716133272e-05</v>
+        <v>3.1202047161333e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.560436046768025e-05</v>
+        <v>3.560436046768194e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.560436046768025e-05</v>
+        <v>3.560436046768194e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.674032447557619e-05</v>
+        <v>3.674032447557613e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.144794491490734e-05</v>
+        <v>3.144794491490413e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.844948504454663e-05</v>
+        <v>2.844948504454432e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.81694995474485e-05</v>
+        <v>2.816949954744731e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.918865369389218e-05</v>
+        <v>2.918865369389097e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>3.560436046768025e-05</v>
+        <v>3.560436046768194e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.560436046768025e-05</v>
+        <v>3.560436046768194e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>3.560436046768025e-05</v>
+        <v>3.560436046768194e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.88435169203479e-05</v>
+        <v>2.884351692034672e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.905786892633645e-05</v>
+        <v>2.905786892633653e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>3.146473529213944e-05</v>
+        <v>3.146473529214115e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.553940897117395e-05</v>
+        <v>2.553940897117093e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.093039338006472e-05</v>
+        <v>4.09303933800647e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.014279994361897e-05</v>
+        <v>3.01427999436157e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.560436046768025e-05</v>
+        <v>3.560436046768194e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.182862829663133e-05</v>
+        <v>4.182862829663124e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7018,85 +7018,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679369e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>1.50883699628279e-05</v>
+        <v>1.508836996282786e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.41399092767938e-05</v>
+        <v>1.413990927679366e-05</v>
       </c>
     </row>
     <row r="9">
@@ -7106,85 +7106,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0002314075111148118</v>
+        <v>0.0002314075111148124</v>
       </c>
       <c r="C9" t="n">
-        <v>5.794758854285052e-05</v>
+        <v>5.794758854285037e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0002539461997646838</v>
+        <v>0.0002539461997646829</v>
       </c>
       <c r="E9" t="n">
-        <v>9.219434277694805e-05</v>
+        <v>9.219434277694819e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001725689650278804</v>
+        <v>0.0001725689650278792</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0003191616699024548</v>
+        <v>0.0003191616699024524</v>
       </c>
       <c r="H9" t="n">
-        <v>8.942970315596084e-05</v>
+        <v>8.942970315596054e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0003474207294269466</v>
+        <v>0.0003474207294269463</v>
       </c>
       <c r="J9" t="n">
-        <v>0.000344469765625872</v>
+        <v>0.0003444697656258712</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0005369166548985911</v>
+        <v>0.0005369166548985908</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002821646578002567</v>
+        <v>0.0002821646578002564</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0008901603577915829</v>
+        <v>0.0008901603577915818</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0001555567568805508</v>
+        <v>0.0001555567568805506</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0002222654289361154</v>
+        <v>0.0002222654289361151</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0003085614664116242</v>
+        <v>0.0003085614664116246</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0001492923943970494</v>
+        <v>0.0001492923943970496</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0001514030015422124</v>
+        <v>0.0001514030015422122</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0003182367777312199</v>
+        <v>0.0003182367777312195</v>
       </c>
       <c r="T9" t="n">
         <v>0.0003136087363239137</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0003629434174037192</v>
+        <v>0.000362943417403718</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0002390143643928248</v>
+        <v>0.0002390143643928244</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0002143107654267482</v>
+        <v>0.0002143107654267479</v>
       </c>
       <c r="X9" t="n">
         <v>0.000411555995781484</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0006709035893831991</v>
+        <v>0.000670903589383197</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0001522740881069949</v>
+        <v>0.000152274088106995</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0004670462368919518</v>
+        <v>0.000467046236891952</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0005252101848526012</v>
+        <v>0.0005252101848525997</v>
       </c>
     </row>
     <row r="10">
@@ -7194,85 +7194,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-2.232625412947764e-07</v>
+        <v>-2.232625412948983e-07</v>
       </c>
       <c r="C10" t="n">
-        <v>1.558661241513276e-05</v>
+        <v>1.55866124151326e-05</v>
       </c>
       <c r="D10" t="n">
-        <v>1.558661241513276e-05</v>
+        <v>1.55866124151326e-05</v>
       </c>
       <c r="E10" t="n">
-        <v>7.168320363425414e-06</v>
+        <v>7.168320363425299e-06</v>
       </c>
       <c r="F10" t="n">
-        <v>2.23973120272233e-06</v>
+        <v>2.239731202722282e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>1.886489297894969e-05</v>
+        <v>1.886489297894951e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>1.558661241513276e-05</v>
+        <v>1.55866124151326e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>1.558661241513276e-05</v>
+        <v>1.55866124151326e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>1.558661241513276e-05</v>
+        <v>1.55866124151326e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>1.558661241513276e-05</v>
+        <v>1.55866124151326e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>1.558661241513276e-05</v>
+        <v>1.55866124151326e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>1.558661241514124e-05</v>
+        <v>1.558661241514111e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>3.331314388840027e-06</v>
+        <v>3.331314388839912e-06</v>
       </c>
       <c r="O10" t="n">
-        <v>6.699176696272703e-06</v>
+        <v>6.69917669627252e-06</v>
       </c>
       <c r="P10" t="n">
-        <v>5.873632265883017e-06</v>
+        <v>5.873632265882827e-06</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.330263812419403e-06</v>
+        <v>-3.330263812419478e-06</v>
       </c>
       <c r="R10" t="n">
-        <v>1.558661241513276e-05</v>
+        <v>1.55866124151326e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>1.558661241513276e-05</v>
+        <v>1.55866124151326e-05</v>
       </c>
       <c r="T10" t="n">
-        <v>1.558661241513276e-05</v>
+        <v>1.55866124151326e-05</v>
       </c>
       <c r="U10" t="n">
-        <v>7.860989803863691e-06</v>
+        <v>7.860989803863474e-06</v>
       </c>
       <c r="V10" t="n">
-        <v>1.125557134626938e-05</v>
+        <v>1.125557134626926e-05</v>
       </c>
       <c r="W10" t="n">
-        <v>1.558971950627873e-05</v>
+        <v>1.55897195062786e-05</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.881257359357896e-06</v>
+        <v>-1.881257359358038e-06</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.129055727107271e-05</v>
+        <v>3.129055727107257e-05</v>
       </c>
       <c r="Z10" t="n">
-        <v>-5.16939085234481e-07</v>
+        <v>-5.169390852345962e-07</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.558661241513276e-05</v>
+        <v>1.55866124151326e-05</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.21013488052694e-05</v>
+        <v>3.210134880526926e-05</v>
       </c>
     </row>
     <row r="11">
@@ -7282,85 +7282,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061911</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061911</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061911</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061911</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061911</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061911</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061911</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061911</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0002887737807060475</v>
+        <v>0.0002887737807060487</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061911</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061915</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061911</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061911</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061911</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061911</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061911</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061911</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0002974909668561993</v>
+        <v>0.0002974909668562033</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061911</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061911</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0002419763169601487</v>
+        <v>0.000241976316960153</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061911</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061911</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061911</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061911</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061911</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0002970247743061867</v>
+        <v>0.0002970247743061911</v>
       </c>
     </row>
     <row r="12">
@@ -7370,85 +7370,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.000403817326519901</v>
+        <v>0.0004038173265199019</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0003185573628550764</v>
+        <v>0.0003185573628550802</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0004148956652326595</v>
+        <v>0.0004148956652326652</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000335390513581441</v>
+        <v>0.0003353905135814459</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0003748966846385943</v>
+        <v>0.0003748966846385995</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0004469507274734729</v>
+        <v>0.000446950727473476</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0003340316228928217</v>
+        <v>0.0003340316228928261</v>
       </c>
       <c r="I12" t="n">
         <v>0.0004608407739610721</v>
       </c>
       <c r="J12" t="n">
-        <v>0.000451139306598895</v>
+        <v>0.0004511393065988969</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0005539828409053391</v>
+        <v>0.000553982840905345</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0004287657550558122</v>
+        <v>0.0004287657550558162</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0007276111051575064</v>
+        <v>0.0007276111051575102</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0003665347516514633</v>
+        <v>0.0003665347516514688</v>
       </c>
       <c r="O12" t="n">
-        <v>0.000399323760612461</v>
+        <v>0.0003993237606124645</v>
       </c>
       <c r="P12" t="n">
-        <v>0.000441740457855757</v>
+        <v>0.0004417404578557612</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0003634556581651565</v>
+        <v>0.0003634556581651606</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0003644930752574687</v>
+        <v>0.0003644930752574671</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0004464961194479184</v>
+        <v>0.0004464961194479227</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0004442213193881939</v>
+        <v>0.0004442213193881981</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0004684705699004265</v>
+        <v>0.0004684705699004313</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0003525078310301404</v>
+        <v>0.0003525078310301326</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0003954138411814004</v>
+        <v>0.0003954138411813987</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0004923648885688924</v>
+        <v>0.0004923648885688962</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0006198408269826688</v>
+        <v>0.0006198408269826711</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0003649212364589785</v>
+        <v>0.0003649212364589842</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0005196397533946159</v>
+        <v>0.000519639753394622</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0005482288131393558</v>
+        <v>0.0005482288131393597</v>
       </c>
     </row>
     <row r="13">
@@ -7458,85 +7458,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0002899649100495667</v>
+        <v>0.0002899649100495678</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0002977358656936361</v>
+        <v>0.0002977358656936383</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0002977358656936361</v>
+        <v>0.0002977358656936383</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0002935980610422439</v>
+        <v>0.0002935980610422468</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0002911755341176969</v>
+        <v>0.0002911755341176985</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0002993472239694259</v>
+        <v>0.0002993472239694297</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0002977358656936361</v>
+        <v>0.0002977358656936383</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0002977358656936361</v>
+        <v>0.0002977358656936383</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0002894848720934969</v>
+        <v>0.0002894848720934981</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0002977358656936361</v>
+        <v>0.0002977358656936383</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0002977358656936361</v>
+        <v>0.0002977358656936383</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0002977358656936403</v>
+        <v>0.0002977358656936426</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0002917120750166293</v>
+        <v>0.0002917120750166282</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0002933674649977974</v>
+        <v>0.0002933674649977978</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0002929616889136448</v>
+        <v>0.0002929616889136485</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0002884377399023952</v>
+        <v>0.0002884377399023987</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0002977358656936361</v>
+        <v>0.0002977358656936383</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0002977358656936361</v>
+        <v>0.0002977358656936383</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0002977358656936361</v>
+        <v>0.0002977358656936383</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0002939385256893375</v>
+        <v>0.0002939385256893402</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0002405585915080316</v>
+        <v>0.0002405585915080298</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0002977373929079592</v>
+        <v>0.0002977373929079608</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0002891499634276122</v>
+        <v>0.0002891499634276136</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.0003054547539991261</v>
+        <v>0.0003054547539991288</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0002898205605589507</v>
+        <v>0.0002898205605589519</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0002977358656936361</v>
+        <v>0.0002977358656936383</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0003058532786595797</v>
+        <v>0.000305853278659586</v>
       </c>
     </row>
     <row r="14">
@@ -7546,85 +7546,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-2.25491803837764e-06</v>
+        <v>-2.254918038377769e-06</v>
       </c>
       <c r="C14" t="n">
-        <v>-2.25491803837764e-06</v>
+        <v>-2.254918038377769e-06</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.25491803837764e-06</v>
+        <v>-2.254918038377769e-06</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.25491803837764e-06</v>
+        <v>-2.254918038377769e-06</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.25491803837764e-06</v>
+        <v>-2.254918038377769e-06</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.815374407221912e-06</v>
+        <v>-5.815374407222027e-06</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.25491803837764e-06</v>
+        <v>-2.254918038377769e-06</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.25491803837764e-06</v>
+        <v>-2.254918038377769e-06</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.673001921707183e-06</v>
+        <v>-5.673001921707325e-06</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.25491803837764e-06</v>
+        <v>-2.254918038377769e-06</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.25491803837764e-06</v>
+        <v>-2.254918038377776e-06</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.25491803837764e-06</v>
+        <v>-2.254918038377769e-06</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.25491803837764e-06</v>
+        <v>-2.254918038377769e-06</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.815374407221912e-06</v>
+        <v>-5.815374407222027e-06</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.815374407221912e-06</v>
+        <v>-5.815374407222027e-06</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.25491803837764e-06</v>
+        <v>-2.254918038377769e-06</v>
       </c>
       <c r="R14" t="n">
-        <v>-2.25491803837764e-06</v>
+        <v>-2.254918038377769e-06</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.788725488365201e-06</v>
+        <v>-1.788725488365296e-06</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.25491803837764e-06</v>
+        <v>-2.254918038377769e-06</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.815374407221919e-06</v>
+        <v>-5.815374407222034e-06</v>
       </c>
       <c r="V14" t="n">
-        <v>-5.59621154780427e-06</v>
+        <v>-5.596211547804358e-06</v>
       </c>
       <c r="W14" t="n">
-        <v>-5.815374407221912e-06</v>
+        <v>-5.815374407222027e-06</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.815374407221912e-06</v>
+        <v>-5.815374407222027e-06</v>
       </c>
       <c r="Y14" t="n">
-        <v>-2.25491803837764e-06</v>
+        <v>-2.254918038377769e-06</v>
       </c>
       <c r="Z14" t="n">
-        <v>-2.25491803837764e-06</v>
+        <v>-2.254918038377769e-06</v>
       </c>
       <c r="AA14" t="n">
-        <v>-2.25491803837764e-06</v>
+        <v>-2.254918038377769e-06</v>
       </c>
       <c r="AB14" t="n">
-        <v>-2.25491803837764e-06</v>
+        <v>-2.254918038377769e-06</v>
       </c>
     </row>
     <row r="15">
@@ -7634,85 +7634,85 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0001045376341753366</v>
+        <v>0.000104537634175337</v>
       </c>
       <c r="C15" t="n">
-        <v>1.927767051051186e-05</v>
+        <v>1.927767051051178e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0001156159728880947</v>
+        <v>0.0001156159728880941</v>
       </c>
       <c r="E15" t="n">
-        <v>3.61108212368766e-05</v>
+        <v>3.611082123687656e-05</v>
       </c>
       <c r="F15" t="n">
-        <v>7.561699229403029e-05</v>
+        <v>7.561699229402993e-05</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0001441105787600634</v>
+        <v>0.0001441105787600622</v>
       </c>
       <c r="H15" t="n">
-        <v>3.475193054825668e-05</v>
+        <v>3.475193054825666e-05</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0001615610816165083</v>
+        <v>0.0001615610816165085</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0001566925239711415</v>
+        <v>0.0001566925239711412</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0002547031485607749</v>
+        <v>0.0002547031485607751</v>
       </c>
       <c r="L15" t="n">
         <v>0.0001294860627112479</v>
       </c>
       <c r="M15" t="n">
-        <v>0.000428331412812942</v>
+        <v>0.0004283314128129414</v>
       </c>
       <c r="N15" t="n">
-        <v>6.725505930689904e-05</v>
+        <v>6.725505930689892e-05</v>
       </c>
       <c r="O15" t="n">
-        <v>9.648361189905315e-05</v>
+        <v>9.648361189905296e-05</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0001389003091423478</v>
+        <v>0.0001389003091423473</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.417596582059169e-05</v>
+        <v>6.417596582059158e-05</v>
       </c>
       <c r="R15" t="n">
-        <v>6.521338291290391e-05</v>
+        <v>6.521338291290394e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0001472164271033531</v>
+        <v>0.0001472164271033529</v>
       </c>
       <c r="T15" t="n">
-        <v>0.00014494162704363</v>
+        <v>0.0001449416270436299</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0001656304211870181</v>
+        <v>0.0001656304211870178</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0001049353025221746</v>
+        <v>0.0001049353025221744</v>
       </c>
       <c r="W15" t="n">
-        <v>9.257369246799172e-05</v>
+        <v>9.257369246799132e-05</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0001895247398554831</v>
+        <v>0.0001895247398554829</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.0003205611346381052</v>
+        <v>0.0003205611346381036</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.564154411441413e-05</v>
+        <v>6.564154411441409e-05</v>
       </c>
       <c r="AA15" t="n">
         <v>0.0002203600610500517</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.000248949120794791</v>
+        <v>0.0002489491207947909</v>
       </c>
     </row>
     <row r="16">
@@ -7722,85 +7722,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-9.314782294997721e-06</v>
+        <v>-9.314782294997776e-06</v>
       </c>
       <c r="C16" t="n">
-        <v>-1.543826650928247e-06</v>
+        <v>-1.543826650928396e-06</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.543826650928247e-06</v>
+        <v>-1.543826650928396e-06</v>
       </c>
       <c r="E16" t="n">
-        <v>-5.681631302320819e-06</v>
+        <v>-5.681631302320934e-06</v>
       </c>
       <c r="F16" t="n">
-        <v>-8.104158226867693e-06</v>
+        <v>-8.104158226867795e-06</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.492924743982906e-06</v>
+        <v>-3.49292474398296e-06</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.543826650928247e-06</v>
+        <v>-1.543826650928396e-06</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.543826650928247e-06</v>
+        <v>-1.543826650928396e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.961910534257708e-06</v>
+        <v>-4.961910534257857e-06</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.543826650928247e-06</v>
+        <v>-1.543826650928396e-06</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.543826650928247e-06</v>
+        <v>-1.543826650928396e-06</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.543826650924059e-06</v>
+        <v>-1.543826650924195e-06</v>
       </c>
       <c r="N16" t="n">
-        <v>-7.56761732793514e-06</v>
+        <v>-7.56761732793516e-06</v>
       </c>
       <c r="O16" t="n">
-        <v>-9.472683715611098e-06</v>
+        <v>-9.472683715611166e-06</v>
       </c>
       <c r="P16" t="n">
-        <v>-9.878459799763974e-06</v>
+        <v>-9.878459799764082e-06</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.084195244216962e-05</v>
+        <v>-1.084195244216973e-05</v>
       </c>
       <c r="R16" t="n">
-        <v>-1.543826650928247e-06</v>
+        <v>-1.543826650928396e-06</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.543826650928247e-06</v>
+        <v>-1.543826650928396e-06</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.543826650928247e-06</v>
+        <v>-1.543826650928396e-06</v>
       </c>
       <c r="U16" t="n">
-        <v>-8.901623024070392e-06</v>
+        <v>-8.901623024070487e-06</v>
       </c>
       <c r="V16" t="n">
-        <v>-7.013936999927554e-06</v>
+        <v>-7.013936999927662e-06</v>
       </c>
       <c r="W16" t="n">
-        <v>-5.102755805449272e-06</v>
+        <v>-5.102755805449381e-06</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.369018528579642e-05</v>
+        <v>-1.369018528579649e-05</v>
       </c>
       <c r="Y16" t="n">
-        <v>6.175061654561435e-06</v>
+        <v>6.175061654561354e-06</v>
       </c>
       <c r="Z16" t="n">
-        <v>-9.459131785613501e-06</v>
+        <v>-9.45913178561365e-06</v>
       </c>
       <c r="AA16" t="n">
-        <v>-1.543826650928247e-06</v>
+        <v>-1.543826650928396e-06</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.573586315015378e-06</v>
+        <v>6.573586315015208e-06</v>
       </c>
     </row>
   </sheetData>
@@ -9448,7 +9448,7 @@
         <v>7.30164605049508e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>8.665245574562671e-05</v>
+        <v>8.665245574562673e-05</v>
       </c>
       <c r="E2" t="n">
         <v>9.849341580812622e-05</v>
@@ -9608,7 +9608,7 @@
         <v>4.873007977395277e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.19003500937595e-05</v>
+        <v>6.190035009375951e-05</v>
       </c>
     </row>
     <row r="4">
@@ -9624,10 +9624,10 @@
         <v>0.0003728595777087669</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003778418359002863</v>
+        <v>0.0003778418359002864</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000381633947460304</v>
+        <v>0.0003816339474603041</v>
       </c>
       <c r="F4" t="n">
         <v>0.0003835852943204253</v>
@@ -9660,13 +9660,13 @@
         <v>0.000394622617730783</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0003859414326131042</v>
+        <v>0.0003859414326131043</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0003695150909617117</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0004009370083323268</v>
+        <v>0.0004009370083323267</v>
       </c>
       <c r="S4" t="n">
         <v>0.0003860588451915979</v>
@@ -9678,7 +9678,7 @@
         <v>0.0003673956977097077</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0003274251340523598</v>
+        <v>0.0003274251340523599</v>
       </c>
       <c r="W4" t="n">
         <v>0.0004207416262749077</v>
@@ -9927,7 +9927,7 @@
         <v>2.418081957878229e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.548779128240971e-05</v>
+        <v>2.54877912824097e-05</v>
       </c>
       <c r="R7" t="n">
         <v>3.124504806396249e-05</v>
@@ -10185,7 +10185,7 @@
         <v>-2.672916826309422e-06</v>
       </c>
       <c r="O10" t="n">
-        <v>3.492986198067789e-07</v>
+        <v>3.492986198067857e-07</v>
       </c>
       <c r="P10" t="n">
         <v>-3.915194129046652e-07</v>
@@ -10328,7 +10328,7 @@
         <v>0.0002922725932264776</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0002994656678725215</v>
+        <v>0.0002994656678725216</v>
       </c>
       <c r="E12" t="n">
         <v>0.0003061559529787343</v>
@@ -10373,7 +10373,7 @@
         <v>0.000332936932382443</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0003113743770315138</v>
+        <v>0.0003113743770315139</v>
       </c>
       <c r="T12" t="n">
         <v>0.0002903188785791386</v>
@@ -10400,7 +10400,7 @@
         <v>0.0003458367719690072</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0002754667593960882</v>
+        <v>0.0002754667593960883</v>
       </c>
     </row>
     <row r="13">
@@ -10592,7 +10592,7 @@
         <v>6.128896084836622e-06</v>
       </c>
       <c r="D15" t="n">
-        <v>1.332197073087812e-05</v>
+        <v>1.332197073087813e-05</v>
       </c>
       <c r="E15" t="n">
         <v>2.00122558370883e-05</v>
@@ -10628,7 +10628,7 @@
         <v>3.410947477891351e-05</v>
       </c>
       <c r="P15" t="n">
-        <v>2.152804702866398e-05</v>
+        <v>2.1528047028664e-05</v>
       </c>
       <c r="Q15" t="n">
         <v>1.254224401389342e-06</v>

--- a/Results/Phase 2/Carbon dioxide/carbon dioxide eutrophication marine results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide eutrophication marine results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0004694516340672569</v>
+        <v>0.000469451634067256</v>
       </c>
       <c r="C2" t="n">
         <v>0.0001191072977357664</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0004349110487975471</v>
+        <v>0.0004349110487975454</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001831442318279111</v>
+        <v>0.0001831442318279104</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000314839160355016</v>
+        <v>0.0003148391603550159</v>
       </c>
       <c r="G2" t="n">
-        <v>0.000423959236039476</v>
+        <v>0.0004239592360394741</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0003915841698125059</v>
+        <v>0.0003915841698125033</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0005125834720094493</v>
+        <v>0.0005125834720094518</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000433497937341676</v>
+        <v>0.0004334979373416757</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007953394102567179</v>
+        <v>0.0007953394102567153</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004683925789692579</v>
+        <v>0.0004683925789692581</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001313847378696397</v>
+        <v>0.001313847378696396</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0005903804944331127</v>
+        <v>0.00059038049443311</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0004311725504302343</v>
+        <v>0.0004311725504302328</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0003560849150140698</v>
+        <v>0.0003560849150140679</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0002836020409579405</v>
+        <v>0.0002836020409579403</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0003168484689729744</v>
+        <v>0.0003168484689729726</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0004111646293297458</v>
+        <v>0.0004111646293297443</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0005181926302504832</v>
+        <v>0.0005181926302504814</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0006453961427226161</v>
+        <v>0.0006453961427226147</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0002452621632712423</v>
+        <v>0.0002452621632712419</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0003647633082104873</v>
+        <v>0.0003647633082104857</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0002773125381218512</v>
+        <v>0.0002773125381218473</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0003241746405543891</v>
+        <v>0.0003241746405543862</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0002688662329200783</v>
+        <v>0.0002688662329200791</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0005676880421801887</v>
+        <v>0.0005676880421801859</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0006525939483350552</v>
+        <v>0.0006525939483350549</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.517806368312826e-05</v>
+        <v>4.517806368313092e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.033478872305289e-05</v>
+        <v>6.033478872305285e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>6.095705988373357e-05</v>
+        <v>6.09570598837299e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>5.091943655375189e-05</v>
+        <v>5.091943655375185e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>4.703530792510796e-05</v>
+        <v>4.703530792510791e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>6.422893753638413e-05</v>
+        <v>6.422893753638193e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>6.095705988373357e-05</v>
+        <v>6.09570598837299e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>6.095705988373357e-05</v>
+        <v>6.09570598837299e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>6.035601994380116e-05</v>
+        <v>6.035601994379927e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>6.095705988373357e-05</v>
+        <v>6.09570598837299e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>6.095705988373357e-05</v>
+        <v>6.09570598837299e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>6.290849440301592e-05</v>
+        <v>6.290849440301587e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.872569805914807e-05</v>
+        <v>4.872569805914795e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>5.208698249060509e-05</v>
+        <v>5.208698249059779e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>5.126305045654882e-05</v>
+        <v>5.126305045654487e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.207713079224174e-05</v>
+        <v>4.207713079224026e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>6.095705988373357e-05</v>
+        <v>6.09570598837299e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>6.095705988373357e-05</v>
+        <v>6.09570598837299e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>6.095705988373357e-05</v>
+        <v>6.09570598837299e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>5.324988563805175e-05</v>
+        <v>5.324988563805629e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>5.492902464000979e-05</v>
+        <v>5.49290246400098e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>6.096016090648817e-05</v>
+        <v>6.096016090648514e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>4.352330714607991e-05</v>
+        <v>4.352330714608129e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.663607951533616e-05</v>
+        <v>7.663607951533609e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.488496072791038e-05</v>
+        <v>4.488496072790881e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.095705988373357e-05</v>
+        <v>6.09570598837299e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.804193708575496e-05</v>
+        <v>7.804193708575491e-05</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0005446918259879238</v>
+        <v>0.0005446918259879211</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0004165999687163075</v>
+        <v>0.0004165999687163057</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0005321021882531449</v>
+        <v>0.0005321021882531416</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004392965867194903</v>
+        <v>0.0004392965867194886</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000487955491110066</v>
+        <v>0.0004879554911100645</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0005281103811055058</v>
+        <v>0.0005281103811055027</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0005163100496329967</v>
+        <v>0.0005163100496329938</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0005604128744382413</v>
+        <v>0.0005604128744382374</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0005219238244234246</v>
+        <v>0.0005219238244234244</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0006634740936415092</v>
+        <v>0.000663474093641506</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005443058128407561</v>
+        <v>0.0005443058128407533</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0008537043190617072</v>
+        <v>0.0008537043190617057</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0005887689755729057</v>
+        <v>0.0005887689755729087</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0005307395494979228</v>
+        <v>0.0005307395494979198</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0005033709881122629</v>
+        <v>0.0005033709881122597</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0004769518316556829</v>
+        <v>0.0004769518316556797</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0004890697642678937</v>
+        <v>0.0004890697642678908</v>
       </c>
       <c r="S4" t="n">
-        <v>0.000523446897201666</v>
+        <v>0.0005234468972016634</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0005624573467510362</v>
+        <v>0.0005624573467510331</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0006088215333480714</v>
+        <v>0.0006088215333480684</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0003999685375349206</v>
+        <v>0.0003999685375349202</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0005065341605255187</v>
+        <v>0.0005065341605255159</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0004746593817269989</v>
+        <v>0.0004746593817269933</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.00049174006778107</v>
+        <v>0.000491740067781062</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0004715808026624764</v>
+        <v>0.0004715808026624733</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0005804978431949441</v>
+        <v>0.0005804978431949412</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0006118278788661553</v>
+        <v>0.0006118278788661537</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0003900490916547065</v>
+        <v>0.0003900490916547032</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0003951780793228181</v>
+        <v>0.0003951780793228165</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0003958003504834996</v>
+        <v>0.0003958003504834999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0003911022015039967</v>
+        <v>0.0003911022015039949</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0003903441316109698</v>
+        <v>0.0003903441316109683</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0003969929114675623</v>
+        <v>0.0003969929114675581</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0003958003504834996</v>
+        <v>0.0003958003504834999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003958003504834996</v>
+        <v>0.0003958003504834999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003859179771855141</v>
+        <v>0.0003859179771855152</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003958003504834996</v>
+        <v>0.0003958003504834999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003958003504834996</v>
+        <v>0.0003958003504834999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003977517850027813</v>
+        <v>0.0003977517850027794</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0003913421627263397</v>
+        <v>0.000391342162726334</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0003925673114314108</v>
+        <v>0.0003925673114314055</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0003922669978800962</v>
+        <v>0.0003922669978800912</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0003889188380289705</v>
+        <v>0.000388918838028972</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0003958003504834996</v>
+        <v>0.0003958003504834999</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003958003504834996</v>
+        <v>0.0003958003504834999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003958003504834996</v>
+        <v>0.0003958003504834999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0003929911759731577</v>
+        <v>0.0003929911759731549</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003305943435083904</v>
+        <v>0.0003305943435083903</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003958014807698783</v>
+        <v>0.0003958014807698762</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0003894459523280846</v>
+        <v>0.0003894459523280785</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0004015151690268736</v>
+        <v>0.0004015151690268698</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0003899422590693184</v>
+        <v>0.0003899422590693167</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0003958003504834996</v>
+        <v>0.0003958003504834999</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0004024104174961301</v>
+        <v>0.0004024104174961285</v>
       </c>
     </row>
     <row r="6">
@@ -938,82 +938,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000188304805235432</v>
+        <v>0.0001883048052354309</v>
       </c>
       <c r="C6" t="n">
-        <v>6.021294796381584e-05</v>
+        <v>6.021294796381586e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001757151675006529</v>
+        <v>0.0001757151675006513</v>
       </c>
       <c r="E6" t="n">
-        <v>8.290956596699887e-05</v>
+        <v>8.290956596699873e-05</v>
       </c>
       <c r="F6" t="n">
         <v>0.0001315684703575745</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001674572947673642</v>
+        <v>0.0001674572947673628</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001599230288805049</v>
+        <v>0.0001599230288805031</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0002040258536857488</v>
+        <v>0.0002040258536857466</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001707285280764463</v>
+        <v>0.0001707285280764449</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0003070870728890169</v>
+        <v>0.0003070870728890157</v>
       </c>
       <c r="L6" t="n">
         <v>0.0001879187920882641</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0004973172983092157</v>
+        <v>0.000497317298309216</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0002323819548204146</v>
+        <v>0.0002323819548204189</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0001700864631597817</v>
+        <v>0.0001700864631597806</v>
       </c>
       <c r="P6" t="n">
-        <v>0.000142717901774121</v>
+        <v>0.0001427179017741197</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0001205648109031909</v>
+        <v>0.0001205648109031901</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0001326827435154026</v>
+        <v>0.0001326827435154011</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001670598764491748</v>
+        <v>0.0001670598764491737</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0002060703259985441</v>
+        <v>0.0002060703259985428</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0002481684470099297</v>
+        <v>0.0002481684470099287</v>
       </c>
       <c r="V6" t="n">
-        <v>0.000101515429582004</v>
+        <v>0.0001015154295820039</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0001458810741873773</v>
+        <v>0.0001458810741873764</v>
       </c>
       <c r="X6" t="n">
-        <v>0.000114006295388858</v>
+        <v>0.0001140062953888549</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001353530470285782</v>
+        <v>0.0001353530470285718</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0001151937819099845</v>
+        <v>0.0001151937819099833</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0002241108224424515</v>
+        <v>0.0002241108224424506</v>
       </c>
       <c r="AB6" t="n">
         <v>0.0002554408581136641</v>
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.366207090221465e-05</v>
+        <v>3.366207090221336e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>3.879105857032635e-05</v>
+        <v>3.879105857032633e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>3.941332973100714e-05</v>
+        <v>3.941332973100869e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>3.471518075150459e-05</v>
+        <v>3.471518075150458e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>3.395711085847798e-05</v>
+        <v>3.395711085847794e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>3.633982512942138e-05</v>
+        <v>3.633982512941941e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>3.941332973100714e-05</v>
+        <v>3.941332973100869e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.941332973100714e-05</v>
+        <v>3.941332973100869e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.472268083853518e-05</v>
+        <v>3.472268083853642e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.941332973100714e-05</v>
+        <v>3.941332973100869e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.941332973100714e-05</v>
+        <v>3.941332973100869e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>4.136476425028902e-05</v>
+        <v>4.136476425028897e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.495514197384774e-05</v>
+        <v>3.49551419738438e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>3.191422509326954e-05</v>
+        <v>3.191422509326598e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>3.161391154195446e-05</v>
+        <v>3.161391154195099e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.253181727647891e-05</v>
+        <v>3.253181727648161e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>3.941332973100714e-05</v>
+        <v>3.941332973100869e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.941332973100714e-05</v>
+        <v>3.941332973100869e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>3.941332973100714e-05</v>
+        <v>3.941332973100869e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>3.233808963501567e-05</v>
+        <v>3.233808963501476e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>3.214123555547404e-05</v>
+        <v>3.214123555547401e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>3.514839443173744e-05</v>
+        <v>3.514839443173698e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.879286598994306e-05</v>
+        <v>2.879286598993827e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.512814827438233e-05</v>
+        <v>4.512814827438028e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.355523831682634e-05</v>
+        <v>3.355523831682609e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.941332973100714e-05</v>
+        <v>3.941332973100869e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.602339674363805e-05</v>
+        <v>4.602339674363801e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.225676385953094e-05</v>
+        <v>4.225676385952423e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>6.517054778600231e-05</v>
+        <v>6.517054778600238e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>7.211872549606283e-05</v>
+        <v>7.211872549605534e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>5.503438906946006e-05</v>
+        <v>5.503438906946001e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>8.721203339904501e-05</v>
+        <v>8.72120333990449e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>9.308213964841601e-05</v>
+        <v>9.308213964841073e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>7.849395917350474e-05</v>
+        <v>7.849395917349811e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>7.924331487850397e-05</v>
+        <v>7.92433148784971e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001044561857956474</v>
+        <v>0.0001044561857956445</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001114802347324171</v>
+        <v>0.0001114802347324102</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001331308110513277</v>
+        <v>0.0001331308110513161</v>
       </c>
       <c r="M2" t="n">
-        <v>8.466430189860583e-05</v>
+        <v>8.466430189860562e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>9.664119671235579e-05</v>
+        <v>9.664119671235829e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0001491440785764048</v>
+        <v>0.0001491440785763957</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0001115773483054479</v>
+        <v>0.0001115773483054464</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.582105872282702e-05</v>
+        <v>6.58210587228202e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0001422605661903165</v>
+        <v>0.0001422605661903101</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0001155579519671959</v>
+        <v>0.0001155579519671897</v>
       </c>
       <c r="T2" t="n">
-        <v>9.003789543345207e-05</v>
+        <v>9.003789543344823e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0001024179294265228</v>
+        <v>0.0001024179294265157</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0001142717546399138</v>
+        <v>0.0001142717546399139</v>
       </c>
       <c r="W2" t="n">
-        <v>0.000171042907482317</v>
+        <v>0.0001710429074823121</v>
       </c>
       <c r="X2" t="n">
-        <v>0.000416374750204992</v>
+        <v>0.000416374750204984</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0002526134712625138</v>
+        <v>0.0002526134712625061</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.828750066310179e-05</v>
+        <v>9.828750066309649e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0002263540664249611</v>
+        <v>0.0002263540664249523</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.092724288342856e-05</v>
+        <v>5.092724288342853e-05</v>
       </c>
     </row>
     <row r="3">
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.529391268580703e-05</v>
+        <v>3.529391268579968e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>4.859819687020631e-05</v>
+        <v>4.85981968702063e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>4.852962215528205e-05</v>
+        <v>4.852962215528115e-05</v>
       </c>
       <c r="E3" t="n">
         <v>4.069152735932878e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>3.698647856502823e-05</v>
+        <v>3.698647856502817e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>5.127413273629802e-05</v>
+        <v>5.127413273629653e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>4.852962215528205e-05</v>
+        <v>4.852962215528115e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>4.852962215528205e-05</v>
+        <v>4.852962215528115e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>4.817464412898634e-05</v>
+        <v>4.817464412898156e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>4.852962215528205e-05</v>
+        <v>4.852962215528115e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>4.852962215528205e-05</v>
+        <v>4.852962215528115e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>4.802466513096907e-05</v>
+        <v>4.802466513096896e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>3.826973303005991e-05</v>
+        <v>3.826973303005449e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>4.108923964599506e-05</v>
+        <v>4.108923964598953e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>4.039811044568458e-05</v>
+        <v>4.039811044567587e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.269279368513131e-05</v>
+        <v>3.269279368512831e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>4.852962215528205e-05</v>
+        <v>4.852962215528115e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>4.852962215528205e-05</v>
+        <v>4.852962215528115e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>4.852962215528205e-05</v>
+        <v>4.852962215528115e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>4.206121415804712e-05</v>
+        <v>4.20612141580435e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>4.408023846031242e-05</v>
+        <v>4.408023846031234e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>4.853222334985283e-05</v>
+        <v>4.853222334984882e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>3.39058727568061e-05</v>
+        <v>3.39058727567969e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.167549936784278e-05</v>
+        <v>6.167549936783996e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.504805258730325e-05</v>
+        <v>3.504805258729691e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.852962215528205e-05</v>
+        <v>4.852962215528115e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.189561447385006e-05</v>
+        <v>6.189561447385003e-05</v>
       </c>
     </row>
     <row r="4">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0003604367795866649</v>
+        <v>0.000360436779586657</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0003688321647971988</v>
+        <v>0.0003688321647972031</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003713211139463225</v>
+        <v>0.0003713211139463124</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003645917210087835</v>
+        <v>0.0003645917210087861</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0003765876875191623</v>
+        <v>0.0003765876875191644</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003789620322400188</v>
+        <v>0.0003789620322400067</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0003736448117599769</v>
+        <v>0.0003736448117599686</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0003739179431150706</v>
+        <v>0.0003739179431150626</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0003737790482358752</v>
+        <v>0.0003737790482358763</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003856679218567981</v>
+        <v>0.0003856679218567898</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003935593026911321</v>
+        <v>0.0003935593026911258</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0003755729231089924</v>
+        <v>0.0003755729231089934</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0003802592667472623</v>
+        <v>0.000380259266747262</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0003993959506667463</v>
+        <v>0.000399395950666739</v>
       </c>
       <c r="P4" t="n">
-        <v>0.000385703318613798</v>
+        <v>0.0003857033186137956</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0003690256883584159</v>
+        <v>0.0003690256883584076</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0003968869912323009</v>
+        <v>0.0003968869912322919</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0003871542019058995</v>
+        <v>0.0003871542019058931</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0003778524409709805</v>
+        <v>0.0003778524409709781</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0003823648179877612</v>
+        <v>0.0003823648179877527</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0003254289829516685</v>
+        <v>0.0003254289829516686</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0004073778166539208</v>
+        <v>0.0004073778166539125</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0004967983924943907</v>
+        <v>0.0004967983924943829</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0004371093293018801</v>
+        <v>0.0004371093293018739</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0003808593252054346</v>
+        <v>0.000380859325205429</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0004275380845920909</v>
+        <v>0.0004275380845920853</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0003633048508333</v>
+        <v>0.0003633048508333015</v>
       </c>
     </row>
     <row r="5">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0003578989020957633</v>
+        <v>0.0003578989020957617</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0003627917374907639</v>
+        <v>0.0003627917374907646</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0003627231627758383</v>
+        <v>0.0003627231627758387</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0003593639163378307</v>
+        <v>0.0003593639163378291</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0003582810625604037</v>
+        <v>0.0003582810625604072</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0003637235046549506</v>
+        <v>0.0003637235046549485</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0003627231627758383</v>
+        <v>0.0003627231627758387</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003627231627758383</v>
+        <v>0.0003627231627758387</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003532650871896065</v>
+        <v>0.0003532650871896062</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003627231627758383</v>
+        <v>0.0003627231627758387</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003627231627758383</v>
+        <v>0.0003627231627758387</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003622182057515286</v>
+        <v>0.0003622182057515272</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0003589835536673958</v>
+        <v>0.0003589835536673953</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0003600112307205904</v>
+        <v>0.0003600112307205843</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0003597593222427277</v>
+        <v>0.0003597593222427194</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0003569508247638983</v>
+        <v>0.0003569508247638975</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0003627231627758383</v>
+        <v>0.0003627231627758387</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003627231627758383</v>
+        <v>0.0003627231627758387</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003627231627758383</v>
+        <v>0.0003627231627758387</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0003603655040167296</v>
+        <v>0.0003603655040167271</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0002998449995346007</v>
+        <v>0.0002998449995346008</v>
       </c>
       <c r="W5" t="n">
-        <v>0.000362724110880719</v>
+        <v>0.0003627241108807148</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0003573929778408317</v>
+        <v>0.0003573929778408269</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0003675146806531375</v>
+        <v>0.0003675146806531328</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0003578092889768924</v>
+        <v>0.0003578092889768921</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0003627231627758383</v>
+        <v>0.0003627231627758387</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0003673026934808857</v>
+        <v>0.0003673026934808891</v>
       </c>
     </row>
     <row r="6">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.869177628466056e-05</v>
+        <v>2.869177628465151e-05</v>
       </c>
       <c r="C6" t="n">
         <v>3.708716149519948e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>3.957611064431897e-05</v>
+        <v>3.957611064431187e-05</v>
       </c>
       <c r="E6" t="n">
         <v>3.284671770678288e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>4.484268421716156e-05</v>
+        <v>4.484268421716149e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>4.311876475994302e-05</v>
+        <v>4.311876475993262e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.189980845797317e-05</v>
+        <v>4.189980845796433e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>4.217293981306625e-05</v>
+        <v>4.217293981305715e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.720277290009075e-05</v>
+        <v>4.720277290008883e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.392291855479291e-05</v>
+        <v>5.392291855478386e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>6.181429938913062e-05</v>
+        <v>6.181429938912837e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>4.382791980699086e-05</v>
+        <v>4.382791980699039e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.85142634452627e-05</v>
+        <v>4.85142634452568e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>6.355268318667114e-05</v>
+        <v>6.355268318666454e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.986005113372149e-05</v>
+        <v>4.986005113372123e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.728068505641141e-05</v>
+        <v>3.72806850564025e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>6.514198793029686e-05</v>
+        <v>6.514198793028619e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>5.540919860389703e-05</v>
+        <v>5.540919860388753e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>4.610743766897756e-05</v>
+        <v>4.61074376689724e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>4.652155050768445e-05</v>
+        <v>4.652155050767758e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>5.057155236174851e-05</v>
+        <v>5.057155236174853e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>7.153454917384472e-05</v>
+        <v>7.153454917383803e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0001609551250143151</v>
+        <v>0.0001609551250143078</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001053643259998778</v>
+        <v>0.0001053643259998698</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.911432190342925e-05</v>
+        <v>4.911432190342404e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.579308129008627e-05</v>
+        <v>9.579308129008474e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.15598475312991e-05</v>
+        <v>3.155984753129907e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.615389879375987e-05</v>
+        <v>2.615389879375461e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>3.104673418876136e-05</v>
+        <v>3.104673418876137e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>3.097815947383674e-05</v>
+        <v>3.097815947383388e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.761891303582558e-05</v>
+        <v>2.761891303582555e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.65360592584039e-05</v>
+        <v>2.653605925840386e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.788023717487752e-05</v>
+        <v>2.788023717487451e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>3.097815947383674e-05</v>
+        <v>3.097815947383388e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.097815947383674e-05</v>
+        <v>3.097815947383388e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.668881185382386e-05</v>
+        <v>2.668881185381916e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.097815947383674e-05</v>
+        <v>3.097815947383388e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.097815947383674e-05</v>
+        <v>3.097815947383388e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.047320244952436e-05</v>
+        <v>3.047320244952392e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.723855036539649e-05</v>
+        <v>2.723855036538938e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.416796324051521e-05</v>
+        <v>2.416796324051017e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.391605476265329e-05</v>
+        <v>2.391605476264493e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.520582146189744e-05</v>
+        <v>2.520582146189198e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>3.097815947383674e-05</v>
+        <v>3.097815947383388e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.097815947383674e-05</v>
+        <v>3.097815947383388e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>3.097815947383674e-05</v>
+        <v>3.097815947383388e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.452223653665453e-05</v>
+        <v>2.452223653665317e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.498756894468045e-05</v>
+        <v>2.498756894468043e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.688084340064368e-05</v>
+        <v>2.688084340063991e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.154971036075954e-05</v>
+        <v>2.154971036075245e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.576967735113562e-05</v>
+        <v>3.57696773511272e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.606428567489149e-05</v>
+        <v>2.606428567488632e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.097815947383674e-05</v>
+        <v>3.097815947383388e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.555769017888586e-05</v>
+        <v>3.555769017888582e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0003767356823987325</v>
+        <v>0.0003767356823987382</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001215582285242272</v>
+        <v>0.0001215582285242316</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0003502671749387365</v>
+        <v>0.0003502671749387359</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000166606928704581</v>
+        <v>0.0001666069287045849</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001958322086284621</v>
+        <v>0.0001958322086284627</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0003988501742280083</v>
+        <v>0.0003988501742280062</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000189754633017547</v>
+        <v>0.0001897546330175469</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0003106671131148247</v>
+        <v>0.0003106671131148244</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004107591345810157</v>
+        <v>0.0004107591345810119</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0006759052015236753</v>
+        <v>0.000675905201523675</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004137934492268405</v>
+        <v>0.0004137934492268661</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001201239979884503</v>
+        <v>0.001201239979884502</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0004095044645693471</v>
+        <v>0.000409504464569347</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0003318891381853394</v>
+        <v>0.0003318891381853392</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0003861568825489304</v>
+        <v>0.0003861568825489307</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0002193041212020985</v>
+        <v>0.0002193041212020983</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0001973366668617976</v>
+        <v>0.0001973366668617975</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0003932503135773729</v>
+        <v>0.0003932503135773746</v>
       </c>
       <c r="T2" t="n">
         <v>0.0003726965926619736</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0005332068626120683</v>
+        <v>0.0005332068626120676</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0001587574886892591</v>
+        <v>0.000158757488689258</v>
       </c>
       <c r="W2" t="n">
         <v>0.0004287614057942012</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0003159853176455412</v>
+        <v>0.0003159853176455382</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0002905883849648563</v>
+        <v>0.0002905883849648564</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0002150045144603896</v>
+        <v>0.000215004514460391</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0004395116740522684</v>
+        <v>0.0004395116740522703</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0006222867980086199</v>
+        <v>0.0006222867980086252</v>
       </c>
     </row>
     <row r="3">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.199173039102533e-05</v>
+        <v>4.199173039102187e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>5.660713483772011e-05</v>
+        <v>5.660713483771561e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>5.702706264377416e-05</v>
+        <v>5.702706264377369e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.764026181987582e-05</v>
+        <v>4.76402618198759e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>4.358435490845434e-05</v>
+        <v>4.358435490845446e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>6.014473673232358e-05</v>
+        <v>6.014473673232227e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>5.702706264377416e-05</v>
+        <v>5.702706264377369e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>5.702706264377416e-05</v>
+        <v>5.702706264377369e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>5.647764581802241e-05</v>
+        <v>5.647764581802228e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>5.702706264377416e-05</v>
+        <v>5.702706264377369e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>5.702706264377416e-05</v>
+        <v>5.702706264377369e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>5.891303270066192e-05</v>
+        <v>5.891303270066205e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.53721647910502e-05</v>
+        <v>4.537216479104948e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>4.857503191769042e-05</v>
+        <v>4.85750319176854e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>4.778993179294547e-05</v>
+        <v>4.778993179294453e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.903694443919309e-05</v>
+        <v>3.903694443918952e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>5.702706264377416e-05</v>
+        <v>5.702706264377369e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>5.702706264377416e-05</v>
+        <v>5.702706264377369e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>5.702706264377416e-05</v>
+        <v>5.702706264377369e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>4.968077310174564e-05</v>
+        <v>4.968077310174246e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>5.132373643569295e-05</v>
+        <v>5.132373643569417e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>5.703001751526246e-05</v>
+        <v>5.70300175152619e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>4.041496251453365e-05</v>
+        <v>4.041496251453278e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.196310261680195e-05</v>
+        <v>7.196310261679832e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.171244137543654e-05</v>
+        <v>4.171244137543364e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.702706264377416e-05</v>
+        <v>5.702706264377369e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.349152052835752e-05</v>
+        <v>7.34915205283575e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0005043712829299835</v>
+        <v>0.000504371282929983</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0004110952283858854</v>
+        <v>0.000411095228385883</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004947238227697219</v>
+        <v>0.0004947238227697209</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004269042224886448</v>
+        <v>0.0004269042224886451</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004379576449870367</v>
+        <v>0.0004379576449870358</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0005124317555202807</v>
+        <v>0.0005124317555202803</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0004362188860728769</v>
+        <v>0.0004362188860728763</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0004802900652423092</v>
+        <v>0.000480290065242308</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0005050039655750341</v>
+        <v>0.0005050039655750315</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0006134150596251673</v>
+        <v>0.0006134150596251665</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005178784037845614</v>
+        <v>0.000517878403784562</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0008060919736626011</v>
+        <v>0.0008060919736626008</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0005163151192407057</v>
+        <v>0.0005163151192407058</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0004880252441789131</v>
+        <v>0.0004880252441789118</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0005078051997554129</v>
+        <v>0.0005078051997554123</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0004469893275285362</v>
+        <v>0.000446989327528536</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00043898244837637</v>
+        <v>0.0004389824483763688</v>
       </c>
       <c r="S4" t="n">
-        <v>0.000510390672070008</v>
+        <v>0.0005103906720700071</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0005028990821503204</v>
+        <v>0.0005028990821503194</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0005614031907403806</v>
+        <v>0.0005614031907403799</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0003477265711092514</v>
+        <v>0.0003477265711092546</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0005233340481907448</v>
+        <v>0.0005233340481907439</v>
       </c>
       <c r="X4" t="n">
-        <v>0.000482228488344244</v>
+        <v>0.0004822284883442454</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0004729716046079757</v>
+        <v>0.0004729716046079749</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0004454221713597152</v>
+        <v>0.0004454221713597134</v>
       </c>
       <c r="AA4" t="n">
         <v>0.0005272523947347865</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.000594354005003996</v>
+        <v>0.0005943540050039963</v>
       </c>
     </row>
     <row r="5">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0003823610431851147</v>
+        <v>0.0003823610431851137</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0003874213174314028</v>
+        <v>0.0003874213174313931</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0003878412452374566</v>
+        <v>0.0003878412452374523</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0003835422693863037</v>
+        <v>0.0003835422693863029</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0003824650900906551</v>
+        <v>0.000382465090090654</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0003889776008331553</v>
+        <v>0.0003889776008331529</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0003878412452374566</v>
+        <v>0.0003878412452374523</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003878412452374566</v>
+        <v>0.0003878412452374523</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003758725231042032</v>
+        <v>0.0003758725231042021</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003878412452374566</v>
+        <v>0.0003878412452374523</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003878412452374566</v>
+        <v>0.0003878412452374523</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003897272152943437</v>
+        <v>0.0003897272152943422</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0003835931718288588</v>
+        <v>0.0003835931718288568</v>
       </c>
       <c r="O5" t="n">
-        <v>0.000384760579286554</v>
+        <v>0.0003847605792865514</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0003844744195101967</v>
+        <v>0.0003844744195101931</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0003812840584025207</v>
+        <v>0.0003812840584025201</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0003878412452374566</v>
+        <v>0.0003878412452374523</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003878412452374566</v>
+        <v>0.0003878412452374523</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003878412452374566</v>
+        <v>0.0003878412452374523</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0003851636089638741</v>
+        <v>0.000385163608963871</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003085682299636386</v>
+        <v>0.0003085682299636392</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003878423222534161</v>
+        <v>0.0003878423222534148</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0003817863298094765</v>
+        <v>0.000381786329809476</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0003932852564197882</v>
+        <v>0.0003932852564197842</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0003822592456185102</v>
+        <v>0.0003822592456185077</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0003878412452374566</v>
+        <v>0.0003878412452374523</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0003943245706419462</v>
+        <v>0.0003943245706419457</v>
       </c>
     </row>
     <row r="6">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0001531302487161581</v>
+        <v>0.0001531302487161579</v>
       </c>
       <c r="C6" t="n">
-        <v>5.985419417205972e-05</v>
+        <v>5.98541941720604e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001434827885558957</v>
+        <v>0.0001434827885558935</v>
       </c>
       <c r="E6" t="n">
-        <v>7.566318827481928e-05</v>
+        <v>7.566318827482051e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>8.67166107732121e-05</v>
+        <v>8.67166107732124e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001570241926273597</v>
+        <v>0.0001570241926273582</v>
       </c>
       <c r="H6" t="n">
-        <v>8.497785185905077e-05</v>
+        <v>8.497785185904845e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001290490310284831</v>
+        <v>0.0001290490310284808</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001611849347418046</v>
+        <v>0.0001611849347418027</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002621740254113407</v>
+        <v>0.0002621740254113387</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001666373695707342</v>
+        <v>0.0001666373695707333</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0004548509394487748</v>
+        <v>0.0004548509394487741</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001650740850268796</v>
+        <v>0.0001650740850268774</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0001326176812859906</v>
+        <v>0.0001326176812859902</v>
       </c>
       <c r="P6" t="n">
         <v>0.0001523976368624918</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.574829331471071e-05</v>
+        <v>9.574829331470817e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>8.774141416254376e-05</v>
+        <v>8.774141416254131e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001591496378561824</v>
+        <v>0.0001591496378561804</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0001516580479364956</v>
+        <v>0.0001516580479364936</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0002059956278474598</v>
+        <v>0.0002059956278474596</v>
       </c>
       <c r="V6" t="n">
-        <v>6.876872272011634e-05</v>
+        <v>6.876872272011492e-05</v>
       </c>
       <c r="W6" t="n">
         <v>0.0001679264852978228</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0001268209254513235</v>
+        <v>0.0001268209254513245</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001217305703941496</v>
+        <v>0.0001217305703941475</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.418113714588926e-05</v>
+        <v>9.418113714588944e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0001760113605209608</v>
+        <v>0.0001760113605209593</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.00024311297079017</v>
+        <v>0.0002431129707901709</v>
       </c>
     </row>
     <row r="7">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.112000897128886e-05</v>
+        <v>3.112000897128512e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>3.618028321757673e-05</v>
+        <v>3.618028321756172e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>3.660021102363088e-05</v>
+        <v>3.66002110236301e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>3.230123517247724e-05</v>
+        <v>3.230123517247728e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>3.122405587682912e-05</v>
+        <v>3.122405587682917e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>3.357003794023387e-05</v>
+        <v>3.357003794023242e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>3.660021102363088e-05</v>
+        <v>3.66002110236301e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.660021102363088e-05</v>
+        <v>3.66002110236301e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.205349227097335e-05</v>
+        <v>3.205349227097211e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.660021102363088e-05</v>
+        <v>3.66002110236301e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.660021102363088e-05</v>
+        <v>3.66002110236301e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.848618108051723e-05</v>
+        <v>3.848618108051733e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.235213761503303e-05</v>
+        <v>3.23521376150302e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.935301639363336e-05</v>
+        <v>2.935301639363039e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.906685661727508e-05</v>
+        <v>2.906685661727248e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.004302418869436e-05</v>
+        <v>3.004302418869042e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>3.660021102363088e-05</v>
+        <v>3.66002110236301e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.660021102363088e-05</v>
+        <v>3.66002110236301e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>3.660021102363088e-05</v>
+        <v>3.66002110236301e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.975604607095277e-05</v>
+        <v>2.975604607095109e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.961038157450346e-05</v>
+        <v>2.961038157450487e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>3.243475936049453e-05</v>
+        <v>3.24347593604945e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.637876691655558e-05</v>
+        <v>2.637876691655589e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.204422220596297e-05</v>
+        <v>4.204422220596052e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.101821140468428e-05</v>
+        <v>3.101821140468202e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.660021102363088e-05</v>
+        <v>3.66002110236301e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.308353642812026e-05</v>
+        <v>4.308353642812034e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2638,85 +2638,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0002960307359406473</v>
+        <v>0.0002960307359406475</v>
       </c>
       <c r="C2" t="n">
         <v>0.0001045586153791281</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0004091891434608132</v>
+        <v>0.000409189143460813</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001757370008529381</v>
+        <v>0.000175737000852938</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001777452791468578</v>
+        <v>0.000177745279146858</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0003747709123372833</v>
+        <v>0.000374770912337283</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001295438655803281</v>
+        <v>0.0001295438655803275</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000385224207348176</v>
+        <v>0.000385224207348175</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0003883624642507679</v>
+        <v>0.0003883624642507681</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004649088928065415</v>
+        <v>0.0004649088928065411</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003409344070427945</v>
+        <v>0.0003409344070427931</v>
       </c>
       <c r="M2" t="n">
         <v>0.00104343646121261</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0002728693055101483</v>
+        <v>0.0002728693055101474</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0002569226500327258</v>
+        <v>0.0002569226500327251</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0003690009022679397</v>
+        <v>0.000369000902267939</v>
       </c>
       <c r="Q2" t="n">
         <v>0.0001834932490540679</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0001312866864511038</v>
+        <v>0.0001312866864511033</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0003598813391129514</v>
+        <v>0.0003598813391129504</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0003171192989499636</v>
+        <v>0.0003171192989499631</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0003787073417644128</v>
+        <v>0.0003787073417644121</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0001901195183427889</v>
+        <v>0.0001901195183427904</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0003710926262078039</v>
+        <v>0.0003710926262078021</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0003926413587856774</v>
+        <v>0.0003926413587856764</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0004607587174204085</v>
+        <v>0.0004607587174204078</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.000209746350345094</v>
+        <v>0.0002097463503450932</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0004424551322414317</v>
+        <v>0.0004424551322414306</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.000575986324572152</v>
+        <v>0.0005759863245721513</v>
       </c>
     </row>
     <row r="3">
@@ -2726,85 +2726,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.134097306721764e-05</v>
+        <v>4.134097306721844e-05</v>
       </c>
       <c r="C3" t="n">
         <v>5.574543155556616e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>5.617397858150432e-05</v>
+        <v>5.61739785815044e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.698050289578366e-05</v>
+        <v>4.698050289578373e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>4.288962584359476e-05</v>
+        <v>4.288962584359477e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>5.924969890279039e-05</v>
+        <v>5.92496989027911e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>5.617397858150432e-05</v>
+        <v>5.61739785815044e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>5.617397858150432e-05</v>
+        <v>5.61739785815044e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>5.565559813845625e-05</v>
+        <v>5.565559813845785e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>5.617397858150432e-05</v>
+        <v>5.61739785815044e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>5.617397858150432e-05</v>
+        <v>5.61739785815044e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>5.767058870098191e-05</v>
+        <v>5.767058870098193e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.46759177996021e-05</v>
+        <v>4.467591779960274e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>4.783568473735444e-05</v>
+        <v>4.783568473735659e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>4.706114951035705e-05</v>
+        <v>4.706114951035773e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.842594893740157e-05</v>
+        <v>3.842594893740323e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>5.617397858150432e-05</v>
+        <v>5.61739785815044e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>5.617397858150432e-05</v>
+        <v>5.61739785815044e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>5.617397858150432e-05</v>
+        <v>5.61739785815044e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>4.892443141877201e-05</v>
+        <v>4.892443141877583e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>5.064956766205536e-05</v>
+        <v>5.064956766205683e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>5.61768936899337e-05</v>
+        <v>5.617689368993487e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>3.97854233650935e-05</v>
+        <v>3.978542336509494e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.090541012988433e-05</v>
+        <v>7.090541012988239e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.106544237468416e-05</v>
+        <v>4.106544237468366e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.617397858150432e-05</v>
+        <v>5.61739785815044e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.231544764670973e-05</v>
+        <v>7.231544764670925e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2814,85 +2814,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.000473971236844074</v>
+        <v>0.0004739712368440734</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0004039095506113185</v>
+        <v>0.0004039095506113188</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000515216147612067</v>
+        <v>0.0005152161476120662</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004293023805849202</v>
+        <v>0.0004293023805849207</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004303732176532633</v>
+        <v>0.0004303732176532642</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0005026711065268143</v>
+        <v>0.0005026711065268135</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0004132887275852722</v>
+        <v>0.0004132887275852709</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0005064812098094971</v>
+        <v>0.0005064812098094965</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0004968972555303928</v>
+        <v>0.000496897255530395</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0005355253419542522</v>
+        <v>0.0005355253419542514</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004903380976752783</v>
+        <v>0.0004903380976752776</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0007473429605295802</v>
+        <v>0.0007473429605295794</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0004655291674274038</v>
+        <v>0.0004655291674274028</v>
       </c>
       <c r="O4" t="n">
-        <v>0.000459716798760967</v>
+        <v>0.0004597167987609653</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0005005680056114169</v>
+        <v>0.0005005680056114158</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0004329526443558056</v>
+        <v>0.0004329526443558055</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0004139239653274337</v>
+        <v>0.0004139239653274332</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0004972440319287414</v>
+        <v>0.0004972440319287402</v>
       </c>
       <c r="T4" t="n">
         <v>0.0004816577704265595</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0005041058888291148</v>
+        <v>0.000504105888829114</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0003650649787460456</v>
+        <v>0.0003650649787460554</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0005013304144252359</v>
+        <v>0.0005013304144252349</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0005091846744118762</v>
+        <v>0.0005091846744118759</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0005340126517598278</v>
+        <v>0.0005340126517598267</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0004425215914969042</v>
+        <v>0.0004425215914969034</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0005273412098936394</v>
+        <v>0.0005273412098936383</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0005764230357745555</v>
+        <v>0.0005764230357745547</v>
       </c>
     </row>
     <row r="5">
@@ -2902,85 +2902,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0003811398089948991</v>
+        <v>0.0003811398089948993</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000386117718300974</v>
+        <v>0.0003861177183009738</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0003865462653269112</v>
+        <v>0.000386546265326912</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0003823721490146712</v>
+        <v>0.0003823721490146709</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0003812199155792544</v>
+        <v>0.0003812199155792554</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0003876673292670884</v>
+        <v>0.0003876673292670904</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0003865462653269112</v>
+        <v>0.000386546265326912</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003865462653269112</v>
+        <v>0.000386546265326912</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003756295096737249</v>
+        <v>0.0003756295096737258</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003865462653269112</v>
+        <v>0.000386546265326912</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003865462653269112</v>
+        <v>0.000386546265326912</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003880428754463856</v>
+        <v>0.0003880428754463863</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0003823553571889556</v>
+        <v>0.0003823553571889574</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00038350705513391</v>
+        <v>0.0003835070551339106</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0003832247461387205</v>
+        <v>0.0003832247461387199</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0003800773169295222</v>
+        <v>0.0003800773169295224</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0003865462653269112</v>
+        <v>0.000386546265326912</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003865462653269112</v>
+        <v>0.000386546265326912</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003865462653269112</v>
+        <v>0.000386546265326912</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0003839038905145761</v>
+        <v>0.0003839038905145776</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003142298194617654</v>
+        <v>0.000314229819461764</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003865473278497031</v>
+        <v>0.0003865473278497044</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0003805728293946625</v>
+        <v>0.0003805728293946639</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0003919156991410926</v>
+        <v>0.0003919156991410916</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0003810393812929148</v>
+        <v>0.0003810393812929145</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0003865462653269112</v>
+        <v>0.000386546265326912</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.000392840915537274</v>
+        <v>0.000392840915537273</v>
       </c>
     </row>
     <row r="6">
@@ -2990,85 +2990,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0001234872540763632</v>
+        <v>0.0001234872540763622</v>
       </c>
       <c r="C6" t="n">
-        <v>5.342556784360791e-05</v>
+        <v>5.342556784360789e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001647321648443553</v>
+        <v>0.0001647321648443546</v>
       </c>
       <c r="E6" t="n">
-        <v>7.881839781721044e-05</v>
+        <v>7.881839781721041e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>7.988923488555245e-05</v>
+        <v>7.988923488555258e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000148036386503525</v>
+        <v>0.0001480363865035238</v>
       </c>
       <c r="H6" t="n">
-        <v>6.28047448175617e-05</v>
+        <v>6.280474481756064e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001559972270417866</v>
+        <v>0.0001559972270417855</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001528278868402031</v>
+        <v>0.0001528278868402047</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0001850413591865432</v>
+        <v>0.0001850413591865424</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001398541149075679</v>
+        <v>0.0001398541149075671</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0003968589777618702</v>
+        <v>0.0003968589777618707</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001150451846596935</v>
+        <v>0.0001150451846596924</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0001050820787376773</v>
+        <v>0.0001050820787376759</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0001459332855881289</v>
+        <v>0.0001459332855881273</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.246866158809465e-05</v>
+        <v>8.246866158809408e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>6.343998255972376e-05</v>
+        <v>6.343998255972237e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001467600491610308</v>
+        <v>0.00014676004916103</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0001311737876588492</v>
+        <v>0.0001311737876588483</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001494711688058256</v>
+        <v>0.0001494711688058246</v>
       </c>
       <c r="V6" t="n">
-        <v>8.006355398337624e-05</v>
+        <v>8.006355398337778e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0001466956944019463</v>
+        <v>0.0001466956944019448</v>
       </c>
       <c r="X6" t="n">
-        <v>0.000154549954388588</v>
+        <v>0.0001545499543885864</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001835286689921171</v>
+        <v>0.0001835286689921163</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.20376087291941e-05</v>
+        <v>9.203760872919272e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0001768572271259281</v>
+        <v>0.0001768572271259271</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0002259390530068438</v>
+        <v>0.0002259390530068436</v>
       </c>
     </row>
     <row r="7">
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.065582622718903e-05</v>
+        <v>3.065582622718806e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>3.563373553326335e-05</v>
+        <v>3.563373553326338e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>3.606228255920103e-05</v>
+        <v>3.606228255920259e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>3.188816624696101e-05</v>
+        <v>3.188816624696103e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>3.073593281154453e-05</v>
+        <v>3.073593281154456e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>3.303260924379932e-05</v>
+        <v>3.303260924380123e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>3.606228255920103e-05</v>
+        <v>3.606228255920259e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.606228255920103e-05</v>
+        <v>3.606228255920259e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.156014098353651e-05</v>
+        <v>3.156014098353664e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.606228255920103e-05</v>
+        <v>3.606228255920259e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.606228255920103e-05</v>
+        <v>3.606228255920259e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75588926786757e-05</v>
+        <v>3.755889267867574e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.187137442124429e-05</v>
+        <v>3.187137442124625e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.887233511062065e-05</v>
+        <v>2.887233511062105e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.859002611543091e-05</v>
+        <v>2.859002611543001e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.959333416181256e-05</v>
+        <v>2.95933341618119e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>3.606228255920103e-05</v>
+        <v>3.606228255920259e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.606228255920103e-05</v>
+        <v>3.606228255920259e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>3.606228255920103e-05</v>
+        <v>3.606228255920259e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.926917049128733e-05</v>
+        <v>2.92691704912881e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.922839469909552e-05</v>
+        <v>2.92283946990961e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>3.191260782641438e-05</v>
+        <v>3.191260782641567e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.593810937137288e-05</v>
+        <v>2.593810937137393e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.143171637338271e-05</v>
+        <v>4.143171637338154e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.055539852520482e-05</v>
+        <v>3.055539852520493e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.606228255920103e-05</v>
+        <v>3.606228255920259e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.235693276956269e-05</v>
+        <v>4.235693276956247e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3322,85 +3322,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0002563455375076487</v>
+        <v>0.0002563455375076426</v>
       </c>
       <c r="C2" t="n">
-        <v>9.460161342395695e-05</v>
+        <v>9.460161342395688e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000277317553834778</v>
+        <v>0.0002773175538347725</v>
       </c>
       <c r="E2" t="n">
         <v>0.0001255513979115397</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002010382488544968</v>
+        <v>0.0002010382488544969</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0003379998732792389</v>
+        <v>0.0003379998732792337</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001242366578448498</v>
+        <v>0.0001242366578448437</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0003642946354521221</v>
+        <v>0.0003642946354521155</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0003611215859185633</v>
+        <v>0.0003611215859185605</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000540618631255605</v>
+        <v>0.0005406186312555997</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003035745367427796</v>
+        <v>0.0003035745367427758</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008704442018156451</v>
+        <v>0.0008704442018156496</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0001857671963744299</v>
+        <v>0.0001857671963744236</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0002478389247364265</v>
+        <v>0.0002478389247364201</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0003281364937306748</v>
+        <v>0.0003281364937306712</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0001799382719714201</v>
+        <v>0.000179938271971414</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0001819021700577794</v>
+        <v>0.000181902170057773</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0003371392706941786</v>
+        <v>0.0003371392706941743</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0003328329261031331</v>
+        <v>0.0003328329261031275</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0003787383358264866</v>
+        <v>0.0003787383358264802</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0002622318284239323</v>
+        <v>0.0002622318284239315</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0002404371927374256</v>
+        <v>0.0002404371927374196</v>
       </c>
       <c r="X2" t="n">
-        <v>0.000423971836465316</v>
+        <v>0.0004239718364653118</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0006652920859221524</v>
+        <v>0.0006652920859221508</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0001827127070833654</v>
+        <v>0.0001827127070833631</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.000475604931036317</v>
+        <v>0.0004756049310363107</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.000530349135038257</v>
+        <v>0.0005303491350382571</v>
       </c>
     </row>
     <row r="3">
@@ -3410,82 +3410,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.08155019121922e-05</v>
+        <v>4.081550191218986e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>5.518516392307948e-05</v>
+        <v>5.518516392307952e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>5.552642679637119e-05</v>
+        <v>5.55264267963654e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.643556477732179e-05</v>
+        <v>4.64355647773217e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>4.254866109451311e-05</v>
+        <v>4.254866109451304e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>5.857683290372448e-05</v>
+        <v>5.85768329037179e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>5.552642679637119e-05</v>
+        <v>5.55264267963654e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>5.552642679637119e-05</v>
+        <v>5.55264267963654e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>5.509921851286298e-05</v>
+        <v>5.509921851286267e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>5.552642679637119e-05</v>
+        <v>5.55264267963654e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>5.552642679637119e-05</v>
+        <v>5.55264267963654e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>5.666239080426644e-05</v>
+        <v>5.666239080427029e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.412299892645348e-05</v>
+        <v>4.412299892645176e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>4.725675991833463e-05</v>
+        <v>4.725675991832763e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>4.648859937706041e-05</v>
+        <v>4.648859937705297e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.792446941253458e-05</v>
+        <v>3.792446941253242e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>5.552642679637119e-05</v>
+        <v>5.55264267963654e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>5.552642679637119e-05</v>
+        <v>5.55264267963654e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>5.552642679637119e-05</v>
+        <v>5.55264267963654e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>4.833781498058535e-05</v>
+        <v>4.833781498057989e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>5.030463067868909e-05</v>
+        <v>5.03046306786885e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>5.552931791249733e-05</v>
+        <v>5.552931791249279e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>3.927275490792352e-05</v>
+        <v>3.927275490792199e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.013878481929266e-05</v>
+        <v>7.013878481928891e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.054223893003763e-05</v>
+        <v>4.054223893003173e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.552642679637119e-05</v>
+        <v>5.55264267963654e-05</v>
       </c>
       <c r="AB3" t="n">
         <v>7.151647084527353e-05</v>
@@ -3498,85 +3498,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0004568517714297956</v>
+        <v>0.0004568517714297915</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0003976811338310521</v>
+        <v>0.0003976811338310515</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004644958251151855</v>
+        <v>0.0004644958251151814</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004083795422016173</v>
+        <v>0.0004083795422016168</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004363378976164849</v>
+        <v>0.0004363378976164841</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004866138179849201</v>
+        <v>0.0004866138179849173</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0004086996360934924</v>
+        <v>0.0004086996360934885</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0004961979500282496</v>
+        <v>0.0004961979500282456</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0004851743237611862</v>
+        <v>0.0004851743237611844</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0005604659759977258</v>
+        <v>0.0005604659759977211</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004740661870600911</v>
+        <v>0.0004740661870600888</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0006814054419256467</v>
+        <v>0.0006814054419256494</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0004311267948594617</v>
+        <v>0.0004311267948594579</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0004537512109643756</v>
+        <v>0.0004537512109643714</v>
       </c>
       <c r="P4" t="n">
-        <v>0.000483018731961118</v>
+        <v>0.0004830187319611154</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.000429002220361251</v>
+        <v>0.000429002220361247</v>
       </c>
       <c r="R4" t="n">
-        <v>0.000429718038152472</v>
+        <v>0.0004297180381524682</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0004863001384483748</v>
+        <v>0.0004863001384483682</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0004847305264125874</v>
+        <v>0.0004847305264125832</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0005014625092082118</v>
+        <v>0.0005014625092082078</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0003942205297666732</v>
+        <v>0.0003942205297666794</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0004510533665662645</v>
+        <v>0.000451053366566261</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0005179495890324844</v>
+        <v>0.0005179495890324818</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0006059079862340635</v>
+        <v>0.0006059079862340607</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0004300134693804963</v>
+        <v>0.000430013469380491</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0005367692456972059</v>
+        <v>0.0005367692456972022</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0005571189497547154</v>
+        <v>0.0005571189497547148</v>
       </c>
     </row>
     <row r="5">
@@ -3586,85 +3586,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0003782936043367109</v>
+        <v>0.0003782936043367059</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0003833143008393012</v>
+        <v>0.0003833143008393003</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0003836555637125895</v>
+        <v>0.000383655563712586</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000379542750049212</v>
+        <v>0.0003795427500492112</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0003785703039566723</v>
+        <v>0.000378570303956672</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0003847674009190458</v>
+        <v>0.0003847674009190392</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0003836555637125895</v>
+        <v>0.000383655563712586</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003836555637125895</v>
+        <v>0.000383655563712586</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003736327643378742</v>
+        <v>0.000373632764337873</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003836555637125895</v>
+        <v>0.000383655563712586</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003836555637125895</v>
+        <v>0.000383655563712586</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003847915277204827</v>
+        <v>0.0003847915277204859</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0003794991481598192</v>
+        <v>0.000379499148159814</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0003806413672428783</v>
+        <v>0.0003806413672428735</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0003803613817457781</v>
+        <v>0.000380361381745775</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0003772398569388053</v>
+        <v>0.0003772398569387984</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0003836555637125895</v>
+        <v>0.000383655563712586</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003836555637125895</v>
+        <v>0.000383655563712586</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003836555637125895</v>
+        <v>0.000383655563712586</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0003810353991186811</v>
+        <v>0.0003810353991186746</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003169755547633295</v>
+        <v>0.0003169755547633371</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003836566174904713</v>
+        <v>0.0003836566174904656</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0003777312911695034</v>
+        <v>0.0003777312911695005</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0003889815966249744</v>
+        <v>0.0003889815966249713</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0003781940031885303</v>
+        <v>0.0003781940031885252</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0003836555637125895</v>
+        <v>0.000383655563712586</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0003898798315415382</v>
+        <v>0.000389879831541538</v>
       </c>
     </row>
     <row r="6">
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0001088005681848907</v>
+        <v>0.0001088005681848855</v>
       </c>
       <c r="C6" t="n">
         <v>4.962993058614578e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001164446218702799</v>
+        <v>0.0001164446218702753</v>
       </c>
       <c r="E6" t="n">
-        <v>6.032833895671016e-05</v>
+        <v>6.032833895671015e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>8.82866943715783e-05</v>
+        <v>8.828669437157817e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001344219357865979</v>
+        <v>0.0001344219357865906</v>
       </c>
       <c r="H6" t="n">
-        <v>6.064843284858734e-05</v>
+        <v>6.064843284858218e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001481467467833444</v>
+        <v>0.0001481467467833394</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001427436065846462</v>
+        <v>0.0001427436065846442</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002124147727528196</v>
+        <v>0.0002124147727528155</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001260149838151871</v>
+        <v>0.0001260149838151824</v>
       </c>
       <c r="M6" t="n">
         <v>0.0003333542386807412</v>
       </c>
       <c r="N6" t="n">
-        <v>8.307559161455669e-05</v>
+        <v>8.30755916145518e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0001015593287660515</v>
+        <v>0.0001015593287660453</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0001308268497627944</v>
+        <v>0.0001308268497627893</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.095101711634562e-05</v>
+        <v>8.095101711634081e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>8.166683490756843e-05</v>
+        <v>8.166683490756317e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001382489352034694</v>
+        <v>0.000138248935203462</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0001366793231676826</v>
+        <v>0.0001366793231676772</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001492706270098887</v>
+        <v>0.0001492706270098823</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0001063028439296795</v>
+        <v>0.0001063028439296791</v>
       </c>
       <c r="W6" t="n">
-        <v>9.886148436794122e-05</v>
+        <v>9.886148436793489e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0001657577068341573</v>
+        <v>0.0001657577068341552</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.000257856782989158</v>
+        <v>0.0002578567829891548</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.196226613559063e-05</v>
+        <v>8.196226613558429e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0001887180424523018</v>
+        <v>0.0001887180424522967</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0002090677465098085</v>
+        <v>0.0002090677465098084</v>
       </c>
     </row>
     <row r="7">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.024240109180174e-05</v>
+        <v>3.024240109179973e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>3.526309759439433e-05</v>
+        <v>3.526309759439434e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>3.560436046768701e-05</v>
+        <v>3.56043604676803e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>3.149154680430496e-05</v>
+        <v>3.14915468043049e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>3.051910071176567e-05</v>
+        <v>3.05191007117656e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>3.257551872071666e-05</v>
+        <v>3.257551872071319e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>3.560436046768701e-05</v>
+        <v>3.56043604676803e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.560436046768701e-05</v>
+        <v>3.56043604676803e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.120204716133329e-05</v>
+        <v>3.120204716133279e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.560436046768701e-05</v>
+        <v>3.56043604676803e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.560436046768701e-05</v>
+        <v>3.56043604676803e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.674032447557619e-05</v>
+        <v>3.674032447557555e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.144794491490968e-05</v>
+        <v>3.144794491490739e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.844948504455176e-05</v>
+        <v>2.844948504454672e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.816949954745363e-05</v>
+        <v>2.816949954744852e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.918865369389603e-05</v>
+        <v>2.918865369389221e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>3.560436046768701e-05</v>
+        <v>3.56043604676803e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.560436046768701e-05</v>
+        <v>3.56043604676803e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>3.560436046768701e-05</v>
+        <v>3.56043604676803e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.884351692035713e-05</v>
+        <v>2.884351692034815e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.90578689263361e-05</v>
+        <v>2.905786892633639e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>3.146473529214325e-05</v>
+        <v>3.146473529213949e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.553940897117904e-05</v>
+        <v>2.553940897117408e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.093039338007058e-05</v>
+        <v>4.093039338006497e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.014279994362477e-05</v>
+        <v>3.014279994361907e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.560436046768701e-05</v>
+        <v>3.56043604676803e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.182862829663134e-05</v>
+        <v>4.182862829663127e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4009,82 +4009,82 @@
         <v>9.931460678254093e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>4.262783184742224e-05</v>
+        <v>4.26278318474222e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002219174353710735</v>
+        <v>0.0002219174353710736</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001183458192282498</v>
+        <v>0.0001183458192282499</v>
       </c>
       <c r="F2" t="n">
-        <v>9.019581770743976e-05</v>
+        <v>9.019581770743979e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001431703896442073</v>
+        <v>0.0001431703896442075</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001607664085202286</v>
+        <v>0.0001607664085202288</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001721894687970554</v>
+        <v>0.0001721894687970555</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001761851667334808</v>
+        <v>0.0001761851667334807</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0003182915867689071</v>
+        <v>0.0003182915867689076</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002352078855958754</v>
+        <v>0.0002352078855958753</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0004202166449323049</v>
+        <v>0.0004202166449323047</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0002598816462480175</v>
+        <v>0.0002598816462480173</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0001153129549264051</v>
+        <v>0.0001153129549264053</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0001917957478722869</v>
+        <v>0.0001917957478722873</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0001698241914095789</v>
+        <v>0.0001698241914095788</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0001476927839188636</v>
+        <v>0.0001476927839188638</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0001693939456756527</v>
+        <v>0.0001693939456756528</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0001336373812910574</v>
+        <v>0.0001336373812910576</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0002338245068082762</v>
+        <v>0.0002338245068082768</v>
       </c>
       <c r="V2" t="n">
-        <v>9.03409063852838e-05</v>
+        <v>9.034090638528332e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0002656530708521649</v>
+        <v>0.0002656530708521653</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0002220664747817375</v>
+        <v>0.0002220664747817379</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0001064808656621198</v>
+        <v>0.0001064808656621194</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0001555592715043606</v>
+        <v>0.000155559271504361</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0002491107901609415</v>
+        <v>0.0002491107901609414</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0002000981561355212</v>
+        <v>0.0002000981561355213</v>
       </c>
     </row>
     <row r="3">
@@ -4094,85 +4094,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.687937853172173e-05</v>
+        <v>3.687937853172236e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>5.028482526083379e-05</v>
+        <v>5.028482526083378e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>5.048848936164057e-05</v>
+        <v>5.048848936164109e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.229770739611678e-05</v>
+        <v>4.22977073961168e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>3.83937010642165e-05</v>
+        <v>3.839370106421648e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>5.331042714721531e-05</v>
+        <v>5.331042714721623e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>5.048848936164057e-05</v>
+        <v>5.048848936164109e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>5.048848936164057e-05</v>
+        <v>5.048848936164109e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>5.003432767228876e-05</v>
+        <v>5.003432767228879e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>5.048848936164057e-05</v>
+        <v>5.048848936164109e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>5.048848936164057e-05</v>
+        <v>5.048848936164109e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>5.067452726991222e-05</v>
+        <v>5.067452726991225e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>3.993915171333647e-05</v>
+        <v>3.993915171333678e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>4.283820129655529e-05</v>
+        <v>4.283820129655572e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>4.212757419294484e-05</v>
+        <v>4.21275741929453e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.420487764129545e-05</v>
+        <v>3.420487764129562e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>5.048848936164057e-05</v>
+        <v>5.048848936164109e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>5.048848936164057e-05</v>
+        <v>5.048848936164109e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>5.048848936164057e-05</v>
+        <v>5.048848936164109e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>4.383747758469406e-05</v>
+        <v>4.383747758469414e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>4.561136346188824e-05</v>
+        <v>4.561136346188773e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>5.049116394008436e-05</v>
+        <v>5.049116394008488e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>3.545217968949336e-05</v>
+        <v>3.545217968949348e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.400502963199408e-05</v>
+        <v>6.400502963199404e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.662658231125252e-05</v>
+        <v>3.662658231125276e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.048848936164057e-05</v>
+        <v>5.048848936164109e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.450548295038185e-05</v>
+        <v>6.450548295038181e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4182,85 +4182,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0003853968774520707</v>
+        <v>0.0003853968774520708</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0003646057827103311</v>
+        <v>0.0003646057827103312</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004300841687974922</v>
+        <v>0.0004300841687974921</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003917333969061039</v>
+        <v>0.0003917333969061041</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0003816881815348335</v>
+        <v>0.0003816881815348338</v>
       </c>
       <c r="G4" t="n">
         <v>0.0004013817953245449</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0004077953375819708</v>
+        <v>0.0004077953375819719</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0004119589089165271</v>
+        <v>0.0004119589089165283</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000403072471462658</v>
+        <v>0.0004030724714626584</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0004652114152995801</v>
+        <v>0.0004652114152995804</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004349283818400854</v>
+        <v>0.0004349283818400855</v>
       </c>
       <c r="M4" t="n">
         <v>0.0005024801314109518</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0004439216778638654</v>
+        <v>0.0004439216778638657</v>
       </c>
       <c r="O4" t="n">
         <v>0.0003912280874884201</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0004191051674108968</v>
+        <v>0.0004191051674108967</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0004110967930832808</v>
+        <v>0.0004110967930832812</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0004030301549330229</v>
+        <v>0.0004030301549330231</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0004109399735654651</v>
+        <v>0.0004109399735654653</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0003979071257220584</v>
+        <v>0.0003979071257220585</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0004344241565164596</v>
+        <v>0.0004344241565164597</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0003143174257132866</v>
+        <v>0.0003143174257132863</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0004460252943605885</v>
+        <v>0.0004460252943605882</v>
       </c>
       <c r="X4" t="n">
-        <v>0.00043013849191257</v>
+        <v>0.0004301384919125703</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0003880088946632167</v>
+        <v>0.0003880088946632168</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0004058973972849757</v>
+        <v>0.0004058973972849761</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0004399958272979052</v>
+        <v>0.0004399958272979051</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0004220049194548404</v>
+        <v>0.0004220049194548406</v>
       </c>
     </row>
     <row r="5">
@@ -4270,85 +4270,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0003626399699061125</v>
+        <v>0.0003626399699061133</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0003673966668965638</v>
+        <v>0.000367396666896564</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000367600330997371</v>
+        <v>0.0003676003309973709</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0003640147531453064</v>
+        <v>0.0003640147531453066</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0003628069183095435</v>
+        <v>0.0003628069183095436</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0003686288941833459</v>
+        <v>0.0003686288941833466</v>
       </c>
       <c r="H5" t="n">
-        <v>0.000367600330997371</v>
+        <v>0.0003676003309973709</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000367600330997371</v>
+        <v>0.0003676003309973709</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000357091971962795</v>
+        <v>0.0003570919719627952</v>
       </c>
       <c r="K5" t="n">
-        <v>0.000367600330997371</v>
+        <v>0.0003676003309973709</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000367600330997371</v>
+        <v>0.0003676003309973709</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003677863689056422</v>
+        <v>0.0003677863689056424</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0003637552213011406</v>
+        <v>0.0003637552213011409</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0003648118908318642</v>
+        <v>0.0003648118908318651</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0003645528755972029</v>
+        <v>0.000364552875597203</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.000361665145737127</v>
+        <v>0.0003616651457371274</v>
       </c>
       <c r="R5" t="n">
-        <v>0.000367600330997371</v>
+        <v>0.0003676003309973709</v>
       </c>
       <c r="S5" t="n">
-        <v>0.000367600330997371</v>
+        <v>0.0003676003309973709</v>
       </c>
       <c r="T5" t="n">
-        <v>0.000367600330997371</v>
+        <v>0.0003676003309973709</v>
       </c>
       <c r="U5" t="n">
         <v>0.0003651761153047969</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0002980140325585203</v>
+        <v>0.0002980140325585202</v>
       </c>
       <c r="W5" t="n">
         <v>0.0003676013058498069</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0003621197726871356</v>
+        <v>0.0003621197726871354</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0003725269512066844</v>
+        <v>0.000372526951206685</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0003625478286522351</v>
+        <v>0.0003625478286522361</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.000367600330997371</v>
+        <v>0.0003676003309973709</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0003725829822884134</v>
+        <v>0.0003725829822884137</v>
       </c>
     </row>
     <row r="6">
@@ -4358,85 +4358,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.015662847946977e-05</v>
+        <v>5.015662847946965e-05</v>
       </c>
       <c r="C6" t="n">
         <v>2.936553373773024e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>9.48439198248909e-05</v>
+        <v>9.484391982489079e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>5.649314793350323e-05</v>
+        <v>5.649314793350319e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>4.644793256223247e-05</v>
+        <v>4.64479325622325e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>6.200945205513303e-05</v>
+        <v>6.200945205513269e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>7.25550886093688e-05</v>
+        <v>7.255508860936962e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>7.6718659943926e-05</v>
+        <v>7.671865994392684e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>7.392218276382294e-05</v>
+        <v>7.392218276382339e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.000129971166326979</v>
+        <v>0.0001299711663269792</v>
       </c>
       <c r="L6" t="n">
-        <v>9.968813286748512e-05</v>
+        <v>9.968813286748471e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0001672398824383507</v>
+        <v>0.0001672398824383506</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001086814288912649</v>
+        <v>0.0001086814288912648</v>
       </c>
       <c r="O6" t="n">
-        <v>5.185574421900796e-05</v>
+        <v>5.185574421900809e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>7.973282414148395e-05</v>
+        <v>7.973282414148381e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.585654411068018e-05</v>
+        <v>7.585654411068029e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>6.7789905960422e-05</v>
+        <v>6.778990596042201e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>7.569972459286461e-05</v>
+        <v>7.569972459286471e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>6.266687674945721e-05</v>
+        <v>6.26668767494572e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>9.505181324704753e-05</v>
+        <v>9.505181324704728e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>4.228504205589135e-05</v>
+        <v>4.228504205589125e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0001066529510911763</v>
+        <v>0.000106652951091176</v>
       </c>
       <c r="X6" t="n">
-        <v>9.076614864315686e-05</v>
+        <v>9.076614864315694e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.276864569061573e-05</v>
+        <v>5.276864569061584e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.065714831237478e-05</v>
+        <v>7.065714831237479e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0001047555783253037</v>
+        <v>0.0001047555783253035</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.676467048223944e-05</v>
+        <v>8.676467048223937e-05</v>
       </c>
     </row>
     <row r="7">
@@ -4446,85 +4446,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.739972093351182e-05</v>
+        <v>2.73997209335124e-05</v>
       </c>
       <c r="C7" t="n">
         <v>3.21564179239626e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>3.23600820247695e-05</v>
+        <v>3.236008202476936e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.877450417270565e-05</v>
+        <v>2.877450417270564e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.756666933694255e-05</v>
+        <v>2.756666933694257e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.925655091393321e-05</v>
+        <v>2.925655091393386e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>3.23600820247695e-05</v>
+        <v>3.236008202476936e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.23600820247695e-05</v>
+        <v>3.236008202476936e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.794168326396047e-05</v>
+        <v>2.794168326396037e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.23600820247695e-05</v>
+        <v>3.236008202476936e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.23600820247695e-05</v>
+        <v>3.236008202476936e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.254611993304073e-05</v>
+        <v>3.254611993304074e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.851497232853939e-05</v>
+        <v>2.851497232853922e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.543954756245196e-05</v>
+        <v>2.543954756245266e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.518053232779074e-05</v>
+        <v>2.518053232779102e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.642489676452613e-05</v>
+        <v>2.642489676452649e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>3.23600820247695e-05</v>
+        <v>3.236008202476936e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.23600820247695e-05</v>
+        <v>3.236008202476936e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>3.23600820247695e-05</v>
+        <v>3.236008202476936e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.580377203538393e-05</v>
+        <v>2.580377203538383e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.598164890112494e-05</v>
+        <v>2.598164890112464e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.822896258039399e-05</v>
+        <v>2.822896258039388e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.274742941772267e-05</v>
+        <v>2.274742941772218e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.728670223408387e-05</v>
+        <v>3.728670223408449e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.730757967963344e-05</v>
+        <v>2.730757967963395e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.23600820247695e-05</v>
+        <v>3.236008202476936e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.734273331581195e-05</v>
+        <v>3.7342733315812e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4690,85 +4690,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.299972548114759e-05</v>
+        <v>6.299972548114637e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>7.301646050495092e-05</v>
+        <v>7.301646050495598e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>8.665245574562658e-05</v>
+        <v>8.665245574562551e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>9.849341580812627e-05</v>
+        <v>9.849341580812616e-05</v>
       </c>
       <c r="F2" t="n">
         <v>0.0001031500006622361</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001026118027461193</v>
+        <v>0.0001026118027461151</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001014372507030912</v>
+        <v>0.0001014372507030898</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000103544975733311</v>
+        <v>0.0001035449757333108</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001112221718006267</v>
+        <v>0.0001112221718006257</v>
       </c>
       <c r="K2" t="n">
-        <v>8.22156654137376e-05</v>
+        <v>8.22156654137363e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001003761134778726</v>
+        <v>0.0001003761134778708</v>
       </c>
       <c r="M2" t="n">
-        <v>6.478395668816808e-05</v>
+        <v>6.478395668816794e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0001267097412128629</v>
+        <v>0.000126709741212862</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0001326917491644862</v>
+        <v>0.0001326917491644847</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0001088742874458816</v>
+        <v>0.00010887428744588</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.380742639458724e-05</v>
+        <v>6.380742639458618e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0001500157382731285</v>
+        <v>0.0001500157382731266</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0001091964173803989</v>
+        <v>0.0001091964173803979</v>
       </c>
       <c r="T2" t="n">
-        <v>6.933698820347859e-05</v>
+        <v>6.933698820347895e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>5.799271711676149e-05</v>
+        <v>5.799271711675999e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>0.000113518660964506</v>
+        <v>0.0001135186609645042</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0002043511456287932</v>
+        <v>0.0002043511456287918</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0003940063099535257</v>
+        <v>0.000394006309953524</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0001279860029228302</v>
+        <v>0.0001279860029228286</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0001361690279338427</v>
+        <v>0.0001361690279338408</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0001744359743248718</v>
+        <v>0.0001744359743248706</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.060154712556888e-05</v>
+        <v>4.060154712556884e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4778,85 +4778,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.552895088228344e-05</v>
+        <v>3.552895088228373e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>4.871104307105222e-05</v>
+        <v>4.871104307103579e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>4.873007977395504e-05</v>
+        <v>4.873007977395073e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.087668290109116e-05</v>
+        <v>4.087668290109102e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>3.716114539025254e-05</v>
+        <v>3.716114539025245e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>5.146741984688104e-05</v>
+        <v>5.146741984688313e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>4.873007977395504e-05</v>
+        <v>4.873007977395073e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>4.873007977395504e-05</v>
+        <v>4.873007977395073e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>4.831774569010284e-05</v>
+        <v>4.831774569010131e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>4.873007977395504e-05</v>
+        <v>4.873007977395073e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>4.873007977395504e-05</v>
+        <v>4.873007977395073e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>4.806006144648404e-05</v>
+        <v>4.806006144648386e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>3.849699638171663e-05</v>
+        <v>3.849699638171548e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>4.130913654943625e-05</v>
+        <v>4.130913654943352e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>4.061981304358242e-05</v>
+        <v>4.06198130435828e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.293462775443487e-05</v>
+        <v>3.293462775443456e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>4.873007977395504e-05</v>
+        <v>4.873007977395073e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>4.873007977395504e-05</v>
+        <v>4.873007977395073e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>4.873007977395504e-05</v>
+        <v>4.873007977395073e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>4.227866396721905e-05</v>
+        <v>4.227866396721817e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>4.416893322987839e-05</v>
+        <v>4.416893322987666e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>4.873267417237073e-05</v>
+        <v>4.87326741723698e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>3.414453744738768e-05</v>
+        <v>3.414453744738621e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.18417691070384e-05</v>
+        <v>6.18417691070371e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.528373313577353e-05</v>
+        <v>3.528373313577144e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.873007977395504e-05</v>
+        <v>4.873007977395073e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.190035009375967e-05</v>
+        <v>6.190035009375944e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4866,85 +4866,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0003692206934632633</v>
+        <v>0.0003692206934632629</v>
       </c>
       <c r="C4" t="n">
-        <v>0.000372859577708766</v>
+        <v>0.0003728595777087426</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003778418359002853</v>
+        <v>0.0003778418359002847</v>
       </c>
       <c r="E4" t="n">
         <v>0.0003816339474603036</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0003835852943204253</v>
+        <v>0.0003835852943204252</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003836588304778482</v>
+        <v>0.0003836588304778492</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0003832307200504535</v>
+        <v>0.0003832307200504528</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0003839989610738133</v>
+        <v>0.0003839989610738113</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0003776006011883931</v>
+        <v>0.0003776006011883942</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003762246779237344</v>
+        <v>0.0003762246779237342</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003828439479923633</v>
+        <v>0.0003828439479923629</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0003694452202718651</v>
+        <v>0.0003694452202718652</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0003924422460766999</v>
+        <v>0.0003924422460766979</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0003946226177307811</v>
+        <v>0.0003946226177307807</v>
       </c>
       <c r="P4" t="n">
         <v>0.0003859414326131058</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0003695150909617104</v>
+        <v>0.000369515090961713</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0004009370083323305</v>
+        <v>0.00040093700833233</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0003860588451915983</v>
+        <v>0.0003860588451915962</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0003715305513096585</v>
+        <v>0.000371530551309659</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0003673956977097059</v>
+        <v>0.000367395697709705</v>
       </c>
       <c r="V4" t="n">
-        <v>0.00032742513405236</v>
+        <v>0.0003274251340523608</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0004207416262749042</v>
+        <v>0.000420741626274904</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0004898687066278924</v>
+        <v>0.0004898687066278907</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0003929074284833592</v>
+        <v>0.0003929074284833591</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0003958900450099429</v>
+        <v>0.0003958900450099426</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0004098378976163025</v>
+        <v>0.0004098378976163023</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0003606631764422927</v>
+        <v>0.0003606631764422929</v>
       </c>
     </row>
     <row r="5">
@@ -4954,85 +4954,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0003592079187000984</v>
+        <v>0.0003592079187000952</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0003640005384627305</v>
+        <v>0.0003640005384626981</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000364019575165632</v>
+        <v>0.0003640195751656309</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0003606333248855258</v>
+        <v>0.0003606333248855261</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0003595331314540475</v>
+        <v>0.0003595331314540472</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0003650173034787454</v>
+        <v>0.0003650173034787443</v>
       </c>
       <c r="H5" t="n">
-        <v>0.000364019575165632</v>
+        <v>0.0003640195751656309</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000364019575165632</v>
+        <v>0.0003640195751656309</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003546726765321727</v>
+        <v>0.0003546726765321731</v>
       </c>
       <c r="K5" t="n">
-        <v>0.000364019575165632</v>
+        <v>0.0003640195751656309</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000364019575165632</v>
+        <v>0.0003640195751656309</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003633495568381638</v>
+        <v>0.000363349556838164</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0003602897364320917</v>
+        <v>0.0003602897364320928</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0003613147285014086</v>
+        <v>0.0003613147285014107</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0003610634781779713</v>
+        <v>0.000361063478177973</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0003582623183840803</v>
+        <v>0.0003582623183840789</v>
       </c>
       <c r="R5" t="n">
-        <v>0.000364019575165632</v>
+        <v>0.0003640195751656309</v>
       </c>
       <c r="S5" t="n">
-        <v>0.000364019575165632</v>
+        <v>0.0003640195751656309</v>
       </c>
       <c r="T5" t="n">
-        <v>0.000364019575165632</v>
+        <v>0.0003640195751656309</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0003616681098604248</v>
+        <v>0.0003616681098604263</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003021479726387047</v>
+        <v>0.0003021479726387046</v>
       </c>
       <c r="W5" t="n">
         <v>0.0003640205207933905</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0003587033162596864</v>
+        <v>0.000358703316259683</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0003687986319623125</v>
+        <v>0.0003687986319623106</v>
       </c>
       <c r="Z5" t="n">
         <v>0.0003591185397109889</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.000364019575165632</v>
+        <v>0.0003640195751656309</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0003684263400210258</v>
+        <v>0.0003684263400210255</v>
       </c>
     </row>
     <row r="6">
@@ -5042,85 +5042,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.64461663615959e-05</v>
+        <v>3.644616636159428e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>4.008505060709675e-05</v>
+        <v>4.008505060708771e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>4.506730879861746e-05</v>
+        <v>4.506730879861533e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>4.885942035863418e-05</v>
+        <v>4.885942035863417e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>5.081076721875503e-05</v>
+        <v>5.081076721875505e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>4.677617187866176e-05</v>
+        <v>4.677617187865879e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>5.045619294878554e-05</v>
+        <v>5.045619294878329e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>5.122443397214222e-05</v>
+        <v>5.122443397214208e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.981789789336944e-05</v>
+        <v>4.981789789336907e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.345015082206626e-05</v>
+        <v>4.345015082206412e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>5.006942089069537e-05</v>
+        <v>5.006942089069361e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>3.667069317019565e-05</v>
+        <v>3.667069317019555e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>5.966771897502892e-05</v>
+        <v>5.966771897502887e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>5.773995913159149e-05</v>
+        <v>5.77399591315907e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.905877401391583e-05</v>
+        <v>4.905877401391484e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.674056386004172e-05</v>
+        <v>3.674056386004265e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>6.81624812306625e-05</v>
+        <v>6.816248123066071e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>5.328431808992712e-05</v>
+        <v>5.328431808992686e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>3.875602420798988e-05</v>
+        <v>3.875602420798872e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>3.051303911051619e-05</v>
+        <v>3.051303911051526e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>5.040727160246671e-05</v>
+        <v>5.040727160246683e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>8.38589676757145e-05</v>
+        <v>8.385896767571335e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0001529860480287025</v>
+        <v>0.0001529860480287</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.013290138169186e-05</v>
+        <v>6.013290138169023e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.311551790827491e-05</v>
+        <v>6.311551790827282e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.706337051463398e-05</v>
+        <v>7.706337051463191e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.788864934062262e-05</v>
+        <v>2.788864934062257e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5130,85 +5130,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.643339159843043e-05</v>
+        <v>2.643339159842616e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>3.12260113610619e-05</v>
+        <v>3.122601136103825e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>3.124504806396149e-05</v>
+        <v>3.12450480639611e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.78587977838563e-05</v>
+        <v>2.785879778385621e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.675860435237769e-05</v>
+        <v>2.675860435237763e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.813464487955534e-05</v>
+        <v>2.813464487955357e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>3.124504806396149e-05</v>
+        <v>3.12450480639611e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.124504806396149e-05</v>
+        <v>3.12450480639611e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.688997323714849e-05</v>
+        <v>2.688997323714703e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.124504806396149e-05</v>
+        <v>3.12450480639611e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.124504806396149e-05</v>
+        <v>3.12450480639611e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.057502973649462e-05</v>
+        <v>3.057502973649453e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.751520933042538e-05</v>
+        <v>2.751520933042366e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.443206990222091e-05</v>
+        <v>2.443206990222022e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.418081957878122e-05</v>
+        <v>2.418081957878194e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.548779128240812e-05</v>
+        <v>2.548779128240929e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>3.124504806396149e-05</v>
+        <v>3.12450480639611e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.124504806396149e-05</v>
+        <v>3.12450480639611e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>3.124504806396149e-05</v>
+        <v>3.12450480639611e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.478545126123536e-05</v>
+        <v>2.478545126123597e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.513011018881304e-05</v>
+        <v>2.513011018881217e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.713786219420074e-05</v>
+        <v>2.713786219419956e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.182065766049301e-05</v>
+        <v>2.182065766049188e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.602410486064094e-05</v>
+        <v>3.602410486064098e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.634401260932127e-05</v>
+        <v>2.634401260931928e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.124504806396149e-05</v>
+        <v>3.12450480639611e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.565181291935654e-05</v>
+        <v>3.565181291935647e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5374,85 +5374,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.528452305174709e-05</v>
+        <v>8.528452305174647e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>7.234575676132156e-05</v>
+        <v>7.234575676132162e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>8.902200881824411e-05</v>
+        <v>8.902200881824238e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001221831553121424</v>
+        <v>0.0001221831553121425</v>
       </c>
       <c r="F2" t="n">
-        <v>9.010901222027144e-05</v>
+        <v>9.010901222027137e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>7.623237870491184e-05</v>
+        <v>7.62323787049106e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>7.194808957683984e-05</v>
+        <v>7.194808957684099e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>7.327718731184369e-05</v>
+        <v>7.327718731184253e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>9.783194380208799e-05</v>
+        <v>9.783194380208974e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>6.598715824466911e-05</v>
+        <v>6.598715824466769e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001053476712245597</v>
+        <v>0.0001053476712245587</v>
       </c>
       <c r="M2" t="n">
-        <v>6.034285985506136e-05</v>
+        <v>6.034285985506183e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>9.246509879483522e-05</v>
+        <v>9.246509879483398e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0002054687457306632</v>
+        <v>0.0002054687457306613</v>
       </c>
       <c r="P2" t="n">
         <v>0.0001313011341252122</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.620406825621191e-05</v>
+        <v>5.620406825621052e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0001550856271208219</v>
+        <v>0.0001550856271208212</v>
       </c>
       <c r="S2" t="n">
-        <v>9.442647313735625e-05</v>
+        <v>9.442647313735341e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>5.971861924184953e-05</v>
+        <v>5.971861924184779e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>6.134330467688412e-05</v>
+        <v>6.134330467688244e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>0.000121896593838013</v>
+        <v>0.0001218965938380131</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0001647329856488513</v>
+        <v>0.0001647329856488503</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0004793761726631241</v>
+        <v>0.0004793761726631227</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0001190023861083287</v>
+        <v>0.0001190023861083275</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.000107192282698896</v>
+        <v>0.0001071922826988933</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.000185046633023058</v>
+        <v>0.0001850466330230574</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.640137870489021e-05</v>
+        <v>5.640137870488921e-05</v>
       </c>
     </row>
     <row r="3">
@@ -5462,85 +5462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.506450858131274e-05</v>
+        <v>3.506450858131298e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>4.825144293040151e-05</v>
+        <v>4.825144293040148e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>4.81966621598854e-05</v>
+        <v>4.819666215988337e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.051814888007107e-05</v>
+        <v>4.051814888007105e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>3.672436989896351e-05</v>
+        <v>3.672436989896349e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>5.091969975231836e-05</v>
+        <v>5.091969975231672e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>4.81966621598854e-05</v>
+        <v>4.819666215988337e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>4.81966621598854e-05</v>
+        <v>4.819666215988337e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7834448715231e-05</v>
+        <v>4.783444871523186e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>4.81966621598854e-05</v>
+        <v>4.819666215988337e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>4.81966621598854e-05</v>
+        <v>4.819666215988337e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>4.759780393984349e-05</v>
+        <v>4.759780393984386e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>3.801704617464368e-05</v>
+        <v>3.801704617464149e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>4.081449303472755e-05</v>
+        <v>4.081449303472209e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>4.012877121360761e-05</v>
+        <v>4.012877121360625e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.248374067674628e-05</v>
+        <v>3.24837406767444e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>4.81966621598854e-05</v>
+        <v>4.819666215988337e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>4.81966621598854e-05</v>
+        <v>4.819666215988337e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>4.81966621598854e-05</v>
+        <v>4.819666215988337e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>4.177936994296734e-05</v>
+        <v>4.177936994296672e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>4.376933905509149e-05</v>
+        <v>4.376933905509142e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>4.8199243002782e-05</v>
+        <v>4.819924300277694e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>3.368732864525904e-05</v>
+        <v>3.368732864525935e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.124055383233515e-05</v>
+        <v>6.124055383233237e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.482057208664601e-05</v>
+        <v>3.482057208664581e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.81966621598854e-05</v>
+        <v>4.819666215988337e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.144566696303663e-05</v>
+        <v>6.144566696303728e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5550,85 +5550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0003755884322023372</v>
+        <v>0.0003755884322023364</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0003709072176470742</v>
+        <v>0.0003709072176470744</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003769507018764528</v>
+        <v>0.0003769507018764509</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003886015709705595</v>
+        <v>0.0003886015709705598</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0003771016103783764</v>
+        <v>0.0003771016103783763</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003722890318835622</v>
+        <v>0.0003722890318835605</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0003707274588050431</v>
+        <v>0.0003707274588050419</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0003712118993223978</v>
+        <v>0.0003712118993223965</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0003709555435184352</v>
+        <v>0.0003709555435184338</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003685547693312568</v>
+        <v>0.0003685547693312533</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003829012141179479</v>
+        <v>0.0003829012141179465</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0003661169074159594</v>
+        <v>0.0003661169074159599</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0003782056677421163</v>
+        <v>0.0003782056677421145</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0004193941700944075</v>
+        <v>0.000419394170094406</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0003923609465842886</v>
+        <v>0.0003923609465842869</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0003649889479093061</v>
+        <v>0.0003649889479093045</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0004010301149895693</v>
+        <v>0.0004010301149895679</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0003789205656583442</v>
+        <v>0.0003789205656583425</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0003662699604736295</v>
+        <v>0.0003662699604736281</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0003668621392366802</v>
+        <v>0.0003668621392366781</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0003285197125831536</v>
+        <v>0.0003285197125831561</v>
       </c>
       <c r="W4" t="n">
-        <v>0.000404546463888032</v>
+        <v>0.0004045464638880308</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0005192302108278949</v>
+        <v>0.0005192302108278922</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.000387878197351324</v>
+        <v>0.0003878781973513221</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0003835735533398219</v>
+        <v>0.0003835735533398192</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0004119505498210408</v>
+        <v>0.0004119505498210378</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0003647630468439812</v>
+        <v>0.0003647630468439792</v>
       </c>
     </row>
     <row r="5">
@@ -5638,85 +5638,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0003572838266410485</v>
+        <v>0.0003572838266410471</v>
       </c>
       <c r="C5" t="n">
         <v>0.0003621251231854214</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0003620703424149044</v>
+        <v>0.0003620703424149039</v>
       </c>
       <c r="E5" t="n">
         <v>0.0003588356350849913</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0003576435351263804</v>
+        <v>0.00035764353512638</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0003630628576418231</v>
+        <v>0.0003630628576418235</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0003620703424149044</v>
+        <v>0.0003620703424149039</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003620703424149044</v>
+        <v>0.0003620703424149039</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003527320436595045</v>
+        <v>0.0003527320436595029</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003620703424149044</v>
+        <v>0.0003620703424149039</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003620703424149044</v>
+        <v>0.0003620703424149039</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003614714841948646</v>
+        <v>0.0003614714841948651</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0003583599919233673</v>
+        <v>0.0003583599919233676</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0003593796284545864</v>
+        <v>0.0003593796284545876</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0003591296909029478</v>
+        <v>0.0003591296909029438</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0003563431670447397</v>
+        <v>0.0003563431670447378</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0003620703424149044</v>
+        <v>0.0003620703424149039</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003620703424149044</v>
+        <v>0.0003620703424149039</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003620703424149044</v>
+        <v>0.0003620703424149039</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0003597313147574876</v>
+        <v>0.0003597313147574863</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003000432456313226</v>
+        <v>0.0003000432456313248</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003620712831018329</v>
+        <v>0.0003620712831018319</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0003567818607260209</v>
+        <v>0.0003567818607260178</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0003668246877604049</v>
+        <v>0.0003668246877604023</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0003571949146531887</v>
+        <v>0.0003571949146531877</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0003620703424149044</v>
+        <v>0.0003620703424149039</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0003666016306810532</v>
+        <v>0.0003666016306810516</v>
       </c>
     </row>
     <row r="6">
@@ -5726,85 +5726,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.433021322292049e-05</v>
+        <v>4.433021322291565e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>3.964899866765318e-05</v>
+        <v>3.964899866765314e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>4.569248289703403e-05</v>
+        <v>4.569248289702981e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>5.734335199113898e-05</v>
+        <v>5.734335199113896e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>4.584339139895566e-05</v>
+        <v>4.584339139895569e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>3.693501174129297e-05</v>
+        <v>3.693501174129206e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>3.946923982562481e-05</v>
+        <v>3.946923982562107e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>3.995368034298075e-05</v>
+        <v>3.995368034297556e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.474143097216179e-05</v>
+        <v>4.474143097216059e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.729655035183834e-05</v>
+        <v>3.729655035183267e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>5.164299513853033e-05</v>
+        <v>5.164299513852529e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>3.485868843653786e-05</v>
+        <v>3.485868843653823e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.694744876269834e-05</v>
+        <v>4.69474487626936e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>8.404014995213898e-05</v>
+        <v>8.404014995213751e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>5.700692644201973e-05</v>
+        <v>5.700692644201755e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.373072892988757e-05</v>
+        <v>3.373072892988361e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>6.977189601015173e-05</v>
+        <v>6.97718960101473e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>4.766234667892597e-05</v>
+        <v>4.766234667892113e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>3.501174149421098e-05</v>
+        <v>3.50117414942071e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>3.150811909441088e-05</v>
+        <v>3.150811909440924e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>5.330404976121159e-05</v>
+        <v>5.330404976121156e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>6.919244374576441e-05</v>
+        <v>6.91924437457628e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0001838761906856283</v>
+        <v>0.0001838761906856243</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.661997837190643e-05</v>
+        <v>5.661997837190111e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.231533436040146e-05</v>
+        <v>5.231533436039871e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.069233084162288e-05</v>
+        <v>8.069233084161782e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.350482786456089e-05</v>
+        <v>3.350482786455976e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5814,85 +5814,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.6025607661627e-05</v>
+        <v>2.602560766162658e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>3.086690420600034e-05</v>
+        <v>3.086690420600028e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>3.081212343548302e-05</v>
+        <v>3.08121234354822e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.757741610557029e-05</v>
+        <v>2.757741610557027e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.638531614695864e-05</v>
+        <v>2.638531614695863e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.770883749955524e-05</v>
+        <v>2.770883749955545e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>3.081212343548302e-05</v>
+        <v>3.08121234354822e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.081212343548302e-05</v>
+        <v>3.08121234354822e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.651793111323065e-05</v>
+        <v>2.651793111322992e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.081212343548302e-05</v>
+        <v>3.08121234354822e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.081212343548302e-05</v>
+        <v>3.08121234354822e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.021326521544343e-05</v>
+        <v>3.021326521544388e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.710177294395039e-05</v>
+        <v>2.710177294394648e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.402560831231941e-05</v>
+        <v>2.402560831231992e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.377567076067852e-05</v>
+        <v>2.377567076067529e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.508494806531825e-05</v>
+        <v>2.508494806531748e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>3.081212343548302e-05</v>
+        <v>3.08121234354822e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.081212343548302e-05</v>
+        <v>3.08121234354822e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>3.081212343548302e-05</v>
+        <v>3.08121234354822e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.437729461521903e-05</v>
+        <v>2.437729461521738e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.482758280938077e-05</v>
+        <v>2.482758280938073e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.671726295956372e-05</v>
+        <v>2.671726295956342e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.142784058375212e-05</v>
+        <v>2.142784058374918e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.556646878098535e-05</v>
+        <v>3.556646878098063e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.593669567376615e-05</v>
+        <v>2.593669567376691e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.081212343548302e-05</v>
+        <v>3.08121234354822e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.534341170163202e-05</v>
+        <v>3.53434117016307e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6058,85 +6058,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0002501629347805014</v>
+        <v>0.0002501629347805077</v>
       </c>
       <c r="C2" t="n">
-        <v>7.673906970975026e-05</v>
+        <v>7.673906970976614e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00028888565949206</v>
+        <v>0.000288885659492067</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001384121307066549</v>
+        <v>0.0001384121307066598</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001562430259204343</v>
+        <v>0.0001562430259204344</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0003836144104567779</v>
+        <v>0.0003836144104567849</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001832368559083924</v>
+        <v>0.0001832368559083991</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0003182058182347917</v>
+        <v>0.0003182058182347972</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0003706755199162358</v>
+        <v>0.0003706755199162385</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004830757524227335</v>
+        <v>0.0004830757524227395</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003764519808858337</v>
+        <v>0.0003764519808858399</v>
       </c>
       <c r="M2" t="n">
         <v>0.001172222444349837</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0004782897311695334</v>
+        <v>0.0004782897311695393</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0002419408875061221</v>
+        <v>0.0002419408875061279</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0003352127531312033</v>
+        <v>0.000335212753131207</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0002037915856228976</v>
+        <v>0.0002037915856229038</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0002139696057136517</v>
+        <v>0.0002139696057136477</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0002863562284710165</v>
+        <v>0.0002863562284710228</v>
       </c>
       <c r="T2" t="n">
-        <v>0.000294592912275652</v>
+        <v>0.0002945929122756585</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0004223404692935228</v>
+        <v>0.0004223404692935317</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0001388154447263771</v>
+        <v>0.0001388154447263776</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0002739483004102363</v>
+        <v>0.0002739483004102445</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0003775066121419256</v>
+        <v>0.0003775066121419336</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0002651725835814299</v>
+        <v>0.0002651725835814362</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0002114457493259612</v>
+        <v>0.0002114457493259666</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0003945413573022424</v>
+        <v>0.000394541357302248</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0005427281987393115</v>
+        <v>0.0005427281987393117</v>
       </c>
     </row>
     <row r="3">
@@ -6146,85 +6146,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.102801839945977e-05</v>
+        <v>4.102801839946916e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>5.526774653628808e-05</v>
+        <v>5.526774653629093e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>5.571974391516995e-05</v>
+        <v>5.571974391517596e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.656406306244263e-05</v>
+        <v>4.656406306244677e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>4.252336989142252e-05</v>
+        <v>4.25233698914225e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>5.876616890840302e-05</v>
+        <v>5.876616890840478e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>5.571974391516995e-05</v>
+        <v>5.571974391517596e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>5.571974391516995e-05</v>
+        <v>5.571974391517596e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>5.519757198353028e-05</v>
+        <v>5.51975719835316e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>5.571974391516995e-05</v>
+        <v>5.571974391517596e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>5.571974391516995e-05</v>
+        <v>5.571974391517596e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>5.76166803428948e-05</v>
+        <v>5.761668034289477e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.433119876780756e-05</v>
+        <v>4.4331198767813e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>4.746086985831492e-05</v>
+        <v>4.746086985831804e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>4.669371185068945e-05</v>
+        <v>4.669371185069749e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.814075901389601e-05</v>
+        <v>3.814075901389721e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>5.571974391516995e-05</v>
+        <v>5.571974391517596e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>5.571974391516995e-05</v>
+        <v>5.571974391517596e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>5.571974391516995e-05</v>
+        <v>5.571974391517596e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>4.853993162831334e-05</v>
+        <v>4.853993162831376e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>5.017829218556625e-05</v>
+        <v>5.017829218556791e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>5.572263125809394e-05</v>
+        <v>5.572263125810362e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>3.948728484903429e-05</v>
+        <v>3.948728484904338e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.031203489840856e-05</v>
+        <v>7.031203489841222e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.075511205541937e-05</v>
+        <v>4.075511205542074e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.571974391516995e-05</v>
+        <v>5.571974391517596e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.163905891775068e-05</v>
+        <v>7.163905891775088e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6234,85 +6234,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.000456117740969381</v>
+        <v>0.0004561177409693947</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0003926195289550313</v>
+        <v>0.0003926195289550473</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004702317194215528</v>
+        <v>0.0004702317194215703</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004145388938925733</v>
+        <v>0.0004145388938925812</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004213807917625037</v>
+        <v>0.0004213807917625078</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0005047592367870404</v>
+        <v>0.0005047592367870516</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0004317239711061929</v>
+        <v>0.000431723971106205</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0004809185729885932</v>
+        <v>0.0004809185729886107</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0004882959969508282</v>
+        <v>0.0004882959969508287</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0005410117279995863</v>
+        <v>0.0005410117279995985</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005021486153139225</v>
+        <v>0.0005021486153139345</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0007934031302127617</v>
+        <v>0.0007934031302127704</v>
       </c>
       <c r="N4" t="n">
-        <v>0.000539267279453094</v>
+        <v>0.0005392672794531055</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0004531209012860242</v>
+        <v>0.000453120901286036</v>
       </c>
       <c r="P4" t="n">
-        <v>0.000487117401052823</v>
+        <v>0.0004871174010528345</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0004392159287213099</v>
+        <v>0.0004392159287213222</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0004429256975280418</v>
+        <v>0.0004429256975280528</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0004693097715164635</v>
+        <v>0.0004693097715164743</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0004723119460432278</v>
+        <v>0.0004723119460432416</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0005188744304886901</v>
+        <v>0.0005188744304887026</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0003384093131124333</v>
+        <v>0.0003384093131124329</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0004647872274395559</v>
+        <v>0.0004647872274395723</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0005025330160226651</v>
+        <v>0.0005025330160226783</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0004615885817051243</v>
+        <v>0.0004615885817051401</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.000442005781511347</v>
+        <v>0.000442005781511362</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0005087419806015219</v>
+        <v>0.0005087419806015372</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0005631182250135394</v>
+        <v>0.0005631182250135453</v>
       </c>
     </row>
     <row r="5">
@@ -6322,85 +6322,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0003798905197346666</v>
+        <v>0.0003798905197346861</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0003847934837873112</v>
+        <v>0.000384793483787321</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0003852454811661932</v>
+        <v>0.0003852454811662027</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0003810613517707209</v>
+        <v>0.0003810613517707343</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0003799313125035486</v>
+        <v>0.0003799313125035518</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0003863558673032981</v>
+        <v>0.0003863558673033102</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0003852454811661932</v>
+        <v>0.0003852454811662027</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003852454811661932</v>
+        <v>0.0003852454811662027</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003733079894584548</v>
+        <v>0.000373307989458469</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003852454811661932</v>
+        <v>0.0003852454811662027</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003852454811661932</v>
+        <v>0.0003852454811662027</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003871424175939158</v>
+        <v>0.0003871424175939207</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0003810944901910291</v>
+        <v>0.0003810944901910395</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0003822352185530655</v>
+        <v>0.0003822352185530687</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0003819555984677099</v>
+        <v>0.0003819555984677182</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0003788381475925405</v>
+        <v>0.0003788381475925541</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0003852454811661932</v>
+        <v>0.0003852454811662027</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003852454811661932</v>
+        <v>0.0003852454811662027</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003852454811661932</v>
+        <v>0.0003852454811662027</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0003826285238972476</v>
+        <v>0.0003826285238972626</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003061021118413025</v>
+        <v>0.0003061021118413042</v>
       </c>
       <c r="W5" t="n">
-        <v>0.000385246533568783</v>
+        <v>0.0003852465335687936</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0003793289404477458</v>
+        <v>0.0003793289404477629</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.000390564199878252</v>
+        <v>0.0003905641998782553</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0003797910485768937</v>
+        <v>0.0003797910485769099</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0003852454811661932</v>
+        <v>0.0003852454811662027</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0003914117653565481</v>
+        <v>0.0003914117653565563</v>
       </c>
     </row>
     <row r="6">
@@ -6410,85 +6410,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0001067202812890702</v>
+        <v>0.000106720281289078</v>
       </c>
       <c r="C6" t="n">
-        <v>4.322206927472545e-05</v>
+        <v>4.322206927472839e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001208342597412424</v>
+        <v>0.0001208342597412509</v>
       </c>
       <c r="E6" t="n">
-        <v>6.514143421226161e-05</v>
+        <v>6.514143421226551e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>7.198333208219207e-05</v>
+        <v>7.1983332082192e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001512021587724185</v>
+        <v>0.0001512021587724252</v>
       </c>
       <c r="H6" t="n">
-        <v>8.232651142588262e-05</v>
+        <v>8.232651142588966e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001315211133082822</v>
+        <v>0.0001315211133082892</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001463231676444557</v>
+        <v>0.0001463231676444609</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0001916142683192752</v>
+        <v>0.0001916142683192812</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001527511556336145</v>
+        <v>0.0001527511556336202</v>
       </c>
       <c r="M6" t="n">
         <v>0.0004440056705324502</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001898698197727826</v>
+        <v>0.0001898698197727892</v>
       </c>
       <c r="O6" t="n">
-        <v>9.956382327140248e-05</v>
+        <v>9.956382327140994e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0001335603230382014</v>
+        <v>0.0001335603230382049</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.981846904099745e-05</v>
+        <v>8.981846904100466e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>9.352823784773141e-05</v>
+        <v>9.352823784773968e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001199123118361518</v>
+        <v>0.0001199123118361583</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0001229144863629169</v>
+        <v>0.0001229144863629239</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001653173524740687</v>
+        <v>0.0001653173524740743</v>
       </c>
       <c r="V6" t="n">
-        <v>6.127488012339032e-05</v>
+        <v>6.127488012338949e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0001112301494249339</v>
+        <v>0.0001112301494249442</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0001489759380080429</v>
+        <v>0.0001489759380080512</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001121911220248143</v>
+        <v>0.0001121911220248211</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.26083218310358e-05</v>
+        <v>9.260832183104285e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0001593445209212121</v>
+        <v>0.000159344520921219</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0002137207653332273</v>
+        <v>0.0002137207653332274</v>
       </c>
     </row>
     <row r="7">
@@ -6498,85 +6498,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.049306005435596e-05</v>
+        <v>3.049306005436523e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>3.539602410699917e-05</v>
+        <v>3.539602410700277e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>3.584802148588203e-05</v>
+        <v>3.584802148588832e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>3.166389209040928e-05</v>
+        <v>3.166389209041286e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>3.053385282323805e-05</v>
+        <v>3.05338528232381e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>3.279878928867601e-05</v>
+        <v>3.279878928868348e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>3.584802148588203e-05</v>
+        <v>3.584802148588832e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.584802148588203e-05</v>
+        <v>3.584802148588832e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.133516015208311e-05</v>
+        <v>3.133516015208654e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.584802148588203e-05</v>
+        <v>3.584802148588832e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.584802148588203e-05</v>
+        <v>3.584802148588832e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.774495791360466e-05</v>
+        <v>3.774495791360474e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.169703051071775e-05</v>
+        <v>3.169703051072196e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.867814053844302e-05</v>
+        <v>2.867814053844351e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.839852045308728e-05</v>
+        <v>2.839852045309088e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.94406879122301e-05</v>
+        <v>2.944068791223656e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>3.584802148588203e-05</v>
+        <v>3.584802148588832e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.584802148588203e-05</v>
+        <v>3.584802148588832e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>3.584802148588203e-05</v>
+        <v>3.584802148588832e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.907144588262464e-05</v>
+        <v>2.907144588263196e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.896767885226011e-05</v>
+        <v>2.896767885225895e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>3.168945555416261e-05</v>
+        <v>3.168945555417046e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.577186243312289e-05</v>
+        <v>2.577186243313244e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.116674019794032e-05</v>
+        <v>4.116674019794024e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.03935888965817e-05</v>
+        <v>3.039358889659037e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.584802148588203e-05</v>
+        <v>3.584802148588832e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.201430567623771e-05</v>
+        <v>4.201430567623781e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6742,82 +6742,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.871383455434655e-05</v>
+        <v>4.871383455434693e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>7.383766096431192e-05</v>
+        <v>7.383766096431197e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>9.966459429475041e-05</v>
+        <v>9.966459429475085e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>9.202998154507251e-05</v>
+        <v>9.202998154507265e-05</v>
       </c>
       <c r="F2" t="n">
         <v>8.36944006514913e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0003429814251251105</v>
+        <v>0.0003429814251251107</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001018631038346585</v>
+        <v>0.0001018631038346586</v>
       </c>
       <c r="I2" t="n">
-        <v>9.771701148817307e-05</v>
+        <v>9.771701148817352e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001987156714709065</v>
+        <v>0.0001987156714709056</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001515770620358305</v>
+        <v>0.000151577062035831</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002247058268045772</v>
+        <v>0.0002247058268045775</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0001580770613306057</v>
+        <v>0.0001580770613306058</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0001411861596784614</v>
+        <v>0.0001411861596784618</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0001013081660907055</v>
+        <v>0.0001013081660907058</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0002439221454930827</v>
+        <v>0.000243922145493083</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0001270140032933015</v>
+        <v>0.000127014003293302</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0001576113383802055</v>
+        <v>0.0001576113383802059</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0001366700151749442</v>
+        <v>0.0001366700151749447</v>
       </c>
       <c r="T2" t="n">
-        <v>9.760400212753172e-05</v>
+        <v>9.760400212753184e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0001130704003369659</v>
+        <v>0.0001130704003369665</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0001021684543629046</v>
+        <v>0.0001021684543629045</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0002320618175430501</v>
+        <v>0.0002320618175430504</v>
       </c>
       <c r="X2" t="n">
-        <v>0.000379833509061242</v>
+        <v>0.0003798335090612424</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0004010693036259196</v>
+        <v>0.0004010693036259198</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0001049691115932552</v>
+        <v>0.0001049691115932555</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0001583557565100929</v>
+        <v>0.0001583557565100928</v>
       </c>
       <c r="AB2" t="n">
         <v>0.0003721464943007392</v>
@@ -6830,85 +6830,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.799924298679636e-05</v>
+        <v>3.799924298679679e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>5.171941834426987e-05</v>
+        <v>5.171941834426983e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>5.179510980613123e-05</v>
+        <v>5.179510980613166e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.348465824501932e-05</v>
+        <v>4.348465824501937e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>3.953551771239053e-05</v>
+        <v>3.953551771239061e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>5.465577266270475e-05</v>
+        <v>5.46557726627052e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>5.179510980613123e-05</v>
+        <v>5.179510980613166e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>5.179510980613123e-05</v>
+        <v>5.179510980613166e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>5.132465963060391e-05</v>
+        <v>5.132465963060423e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>5.179510980613123e-05</v>
+        <v>5.179510980613166e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>5.179510980613123e-05</v>
+        <v>5.179510980613166e-05</v>
       </c>
       <c r="M3" t="n">
         <v>5.129352639410966e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.110100502239514e-05</v>
+        <v>4.110100502239549e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>4.40398378713312e-05</v>
+        <v>4.403983787133136e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>4.331945892800574e-05</v>
+        <v>4.331945892800624e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.528804028201394e-05</v>
+        <v>3.528804028201431e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>5.179510980613123e-05</v>
+        <v>5.179510980613166e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>5.179510980613123e-05</v>
+        <v>5.179510980613166e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>5.179510980613123e-05</v>
+        <v>5.179510980613166e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>4.505099205418198e-05</v>
+        <v>4.50509920541823e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>4.689814878994779e-05</v>
+        <v>4.689814878994785e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>5.17978210873067e-05</v>
+        <v>5.179782108730727e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>3.655245888762228e-05</v>
+        <v>3.655245888762258e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.549399651506013e-05</v>
+        <v>6.549399651506046e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.774297767796981e-05</v>
+        <v>3.774297767797016e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.179510980613123e-05</v>
+        <v>5.179510980613166e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.661678343563876e-05</v>
+        <v>6.661678343563891e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6918,85 +6918,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0003753600288845181</v>
+        <v>0.0003753600288845187</v>
       </c>
       <c r="C4" t="n">
         <v>0.0003844692657792589</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003939309825158686</v>
+        <v>0.0003939309825158689</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003905352669727751</v>
+        <v>0.0003905352669727752</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0003877204911301355</v>
+        <v>0.0003877204911301354</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004826171101830541</v>
+        <v>0.0004826171101830539</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0003947323134269625</v>
+        <v>0.000394732313426963</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0003932211114525426</v>
+        <v>0.0003932211114525433</v>
       </c>
       <c r="J4" t="n">
         <v>0.0004192529604088911</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0004128524674205188</v>
+        <v>0.0004128524674205193</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004395070434574161</v>
+        <v>0.0004395070434574167</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0004149028786883897</v>
+        <v>0.0004149028786883895</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0004090651055273936</v>
+        <v>0.0004090651055273942</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0003945300451356995</v>
+        <v>0.0003945300451357</v>
       </c>
       <c r="P4" t="n">
-        <v>0.00044651116596997</v>
+        <v>0.0004465111659699709</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.000403899520942865</v>
+        <v>0.0004038995209428656</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0004150518902899941</v>
+        <v>0.0004150518902899945</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0004074190238871078</v>
+        <v>0.0004074190238871084</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0003931799208676113</v>
+        <v>0.000393179920867612</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0003988172413993326</v>
+        <v>0.0003988172413993336</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0003242019783332904</v>
+        <v>0.0003242019783332852</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0004421882157031858</v>
+        <v>0.0004421882157031863</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0004960492620387565</v>
+        <v>0.0004960492620387572</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0005037894597942926</v>
+        <v>0.0005037894597942931</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0003958644167823859</v>
+        <v>0.0003958644167823864</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0004153232219569381</v>
+        <v>0.0004153232219569387</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0004935084637039979</v>
+        <v>0.000493508463703998</v>
       </c>
     </row>
     <row r="5">
@@ -7006,85 +7006,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0003714546860752341</v>
+        <v>0.0003714546860752342</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0003764074260697713</v>
+        <v>0.0003764074260697714</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0003764831175316342</v>
+        <v>0.0003764831175316345</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000372841066677873</v>
+        <v>0.0003728410666778733</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0003716250968386166</v>
+        <v>0.0003716250968386169</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0003775257955512548</v>
+        <v>0.0003775257955512547</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0003764831175316342</v>
+        <v>0.0003764831175316345</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003764831175316342</v>
+        <v>0.0003764831175316345</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003655306673457445</v>
+        <v>0.0003655306673457448</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003764831175316342</v>
+        <v>0.0003764831175316345</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003764831175316342</v>
+        <v>0.0003764831175316345</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003759815341196118</v>
+        <v>0.0003759815341196117</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0003725852419144803</v>
+        <v>0.0003725852419144805</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0003736564119783994</v>
+        <v>0.0003736564119783997</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0003733938423126743</v>
+        <v>0.0003733938423126749</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0003704664845258895</v>
+        <v>0.0003704664845258902</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0003764831175316342</v>
+        <v>0.0003764831175316345</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003764831175316342</v>
+        <v>0.0003764831175316345</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003764831175316342</v>
+        <v>0.0003764831175316345</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0003740249658044768</v>
+        <v>0.0003740249658044772</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003040566009686432</v>
+        <v>0.0003040566009686368</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003764841057617841</v>
+        <v>0.0003764841057617849</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0003709273502600803</v>
+        <v>0.0003709273502600808</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0003814762008765888</v>
+        <v>0.000381476200876589</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0003713612803793856</v>
+        <v>0.0003713612803793858</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0003764831175316342</v>
+        <v>0.0003764831175316345</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0003821464718046696</v>
+        <v>0.0003821464718046699</v>
       </c>
     </row>
     <row r="6">
@@ -7094,82 +7094,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.2232439469615e-05</v>
+        <v>3.223243946961542e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>4.134167636435618e-05</v>
+        <v>4.134167636435611e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>5.080339310096488e-05</v>
+        <v>5.080339310096522e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>4.740767755787264e-05</v>
+        <v>4.740767755787263e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>4.459290171523226e-05</v>
+        <v>4.459290171523229e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001353631229672517</v>
+        <v>0.000135363122967252</v>
       </c>
       <c r="H6" t="n">
-        <v>5.160472401205896e-05</v>
+        <v>5.160472401205921e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>5.009352203763947e-05</v>
+        <v>5.009352203763976e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>8.264699645513827e-05</v>
+        <v>8.264699645513864e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>6.972487800561571e-05</v>
+        <v>6.972487800561598e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>9.637945404251296e-05</v>
+        <v>9.637945404251332e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>7.177528927348683e-05</v>
+        <v>7.177528927348685e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>6.593751611249054e-05</v>
+        <v>6.593751611249109e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>4.727605791989644e-05</v>
+        <v>4.727605791989697e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>9.925717875416703e-05</v>
+        <v>9.92571787541675e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.077193152796206e-05</v>
+        <v>6.077193152796232e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>7.192430087509018e-05</v>
+        <v>7.192430087509042e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>6.429143447220466e-05</v>
+        <v>6.429143447220496e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>5.005233145270837e-05</v>
+        <v>5.005233145270904e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>5.156325418353058e-05</v>
+        <v>5.156325418353117e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>4.713776380032956e-05</v>
+        <v>4.713776380032955e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>9.493422848738236e-05</v>
+        <v>9.493422848738287e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0001487952748229539</v>
+        <v>0.0001487952748229542</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001606618703793891</v>
+        <v>0.0001606618703793894</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.273682736748291e-05</v>
+        <v>5.273682736748321e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.219563254203495e-05</v>
+        <v>7.219563254203517e-05</v>
       </c>
       <c r="AB6" t="n">
         <v>0.0001503808742890936</v>
@@ -7182,85 +7182,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.832709666032977e-05</v>
+        <v>2.832709666032986e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>3.327983665486857e-05</v>
+        <v>3.327983665486867e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>3.335552811673029e-05</v>
+        <v>3.335552811673025e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.971347726296993e-05</v>
+        <v>2.971347726296995e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.849750742371347e-05</v>
+        <v>2.849750742371346e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>3.027180833545236e-05</v>
+        <v>3.027180833545266e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>3.335552811673029e-05</v>
+        <v>3.335552811673025e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.335552811673029e-05</v>
+        <v>3.335552811673025e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.892470339199145e-05</v>
+        <v>2.892470339199176e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.335552811673029e-05</v>
+        <v>3.335552811673025e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.335552811673029e-05</v>
+        <v>3.335552811673025e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.285394470470877e-05</v>
+        <v>3.285394470470872e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.945765249957697e-05</v>
+        <v>2.945765249957683e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.640242476259668e-05</v>
+        <v>2.640242476259696e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.613985509687136e-05</v>
+        <v>2.613985509687155e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.733889511098592e-05</v>
+        <v>2.733889511098619e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>3.335552811673029e-05</v>
+        <v>3.335552811673025e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.335552811673029e-05</v>
+        <v>3.335552811673025e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>3.335552811673029e-05</v>
+        <v>3.335552811673025e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.677097858867414e-05</v>
+        <v>2.677097858867425e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.699238643568217e-05</v>
+        <v>2.699238643568229e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.92301185459815e-05</v>
+        <v>2.923011854598187e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.367336304427759e-05</v>
+        <v>2.367336304427812e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.834861146168554e-05</v>
+        <v>3.834861146168556e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.823369096448163e-05</v>
+        <v>2.823369096448173e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.335552811673029e-05</v>
+        <v>3.335552811673025e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.901888238976559e-05</v>
+        <v>3.901888238976564e-05</v>
       </c>
     </row>
   </sheetData>
